--- a/графики/график Останкино.xlsx
+++ b/графики/график Останкино.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0653134-80DC-4593-BA47-65238F95C72B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA912B4-D87E-4B0F-9CEA-EF61387D717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$2:$M$1658</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$A$1:$H$1329</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -35,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7142" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7150" uniqueCount="654">
   <si>
     <t>№ п/п</t>
   </si>
@@ -1985,6 +1979,30 @@
   </si>
   <si>
     <t>Догружаем в Останкино Крым</t>
+  </si>
+  <si>
+    <t>ТН 8005872169 от 28.06.2026 Донецк НВ 5 317,954 КГ</t>
+  </si>
+  <si>
+    <t>ТН 8005872166 от 28.06.2026 Луганск ЛП 8 670,439 КГ</t>
+  </si>
+  <si>
+    <t>ТН 8005871634 от 27.06.2026 Донецк НВ 5 321,843 КГ</t>
+  </si>
+  <si>
+    <t>ТН 8005871633 от 27.06.2026 ПРС ЛП 1 538,460 КГ</t>
+  </si>
+  <si>
+    <t>ТН 8005871321 от 27.06.2026 Малахутин ЛП 2 040,864 КГ</t>
+  </si>
+  <si>
+    <t>ТН 8005872165 от 28.06.2026 Донецк НВ 304,102 КГ</t>
+  </si>
+  <si>
+    <t>ТН 8005870919 от 28.06.2026 Мелитополь НВ 3 305,454 КГ</t>
+  </si>
+  <si>
+    <t>ТН 8005870918 от 28.06.2026 Бердянск НВ 3 532,555 КГ</t>
   </si>
 </sst>
 </file>
@@ -2957,7 +2975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="442">
+  <cellXfs count="441">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3880,9 +3898,6 @@
     <xf numFmtId="49" fontId="6" fillId="9" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4001,6 +4016,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4265,9 +4283,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4680,7 +4695,7 @@
     <col min="8" max="8" width="24.28515625" style="5" customWidth="1"/>
     <col min="9" max="9" width="9.85546875" style="1" customWidth="1"/>
     <col min="10" max="12" width="16.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.5703125" style="2" customWidth="1"/>
     <col min="14" max="14" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="1020" width="9.140625" style="2"/>
   </cols>
@@ -6277,7 +6292,7 @@
       <c r="E57" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="333" t="s">
+      <c r="F57" s="332" t="s">
         <v>58</v>
       </c>
       <c r="G57" s="94" t="s">
@@ -6311,7 +6326,7 @@
       <c r="E58" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F58" s="334"/>
+      <c r="F58" s="333"/>
       <c r="G58" s="98" t="s">
         <v>57</v>
       </c>
@@ -6739,7 +6754,7 @@
       <c r="E73" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F73" s="333" t="s">
+      <c r="F73" s="332" t="s">
         <v>68</v>
       </c>
       <c r="G73" s="94" t="s">
@@ -6768,7 +6783,7 @@
       <c r="E74" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="F74" s="348"/>
+      <c r="F74" s="347"/>
       <c r="G74" s="144" t="s">
         <v>69</v>
       </c>
@@ -7062,7 +7077,7 @@
       <c r="E85" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="333" t="s">
+      <c r="F85" s="332" t="s">
         <v>72</v>
       </c>
       <c r="G85" s="94" t="s">
@@ -7088,7 +7103,7 @@
       <c r="E86" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="F86" s="348"/>
+      <c r="F86" s="347"/>
       <c r="G86" s="144" t="s">
         <v>71</v>
       </c>
@@ -7112,7 +7127,7 @@
       <c r="E87" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F87" s="333" t="s">
+      <c r="F87" s="332" t="s">
         <v>72</v>
       </c>
       <c r="G87" s="94" t="s">
@@ -7138,7 +7153,7 @@
       <c r="E88" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F88" s="348"/>
+      <c r="F88" s="347"/>
       <c r="G88" s="136" t="s">
         <v>73</v>
       </c>
@@ -7162,7 +7177,7 @@
       <c r="E89" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="F89" s="334"/>
+      <c r="F89" s="333"/>
       <c r="G89" s="98" t="s">
         <v>73</v>
       </c>
@@ -7288,7 +7303,7 @@
       <c r="E94" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F94" s="333" t="s">
+      <c r="F94" s="332" t="s">
         <v>76</v>
       </c>
       <c r="G94" s="94" t="s">
@@ -7314,7 +7329,7 @@
       <c r="E95" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="348"/>
+      <c r="F95" s="347"/>
       <c r="G95" s="144" t="s">
         <v>74</v>
       </c>
@@ -7560,7 +7575,7 @@
       <c r="E105" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F105" s="333" t="s">
+      <c r="F105" s="332" t="s">
         <v>82</v>
       </c>
       <c r="G105" s="94" t="s">
@@ -7586,7 +7601,7 @@
       <c r="E106" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="F106" s="348"/>
+      <c r="F106" s="347"/>
       <c r="G106" s="144" t="s">
         <v>81</v>
       </c>
@@ -7610,7 +7625,7 @@
       <c r="E107" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F107" s="333" t="s">
+      <c r="F107" s="332" t="s">
         <v>84</v>
       </c>
       <c r="G107" s="94" t="s">
@@ -7638,7 +7653,7 @@
       <c r="E108" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F108" s="348"/>
+      <c r="F108" s="347"/>
       <c r="G108" s="136" t="s">
         <v>83</v>
       </c>
@@ -7662,7 +7677,7 @@
       <c r="E109" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="F109" s="348"/>
+      <c r="F109" s="347"/>
       <c r="G109" s="144" t="s">
         <v>83</v>
       </c>
@@ -7686,7 +7701,7 @@
       <c r="E110" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="F110" s="348"/>
+      <c r="F110" s="347"/>
       <c r="G110" s="94" t="s">
         <v>83</v>
       </c>
@@ -7710,7 +7725,7 @@
       <c r="E111" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F111" s="348"/>
+      <c r="F111" s="347"/>
       <c r="G111" s="136" t="s">
         <v>83</v>
       </c>
@@ -7734,7 +7749,7 @@
       <c r="E112" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F112" s="334"/>
+      <c r="F112" s="333"/>
       <c r="G112" s="98" t="s">
         <v>83</v>
       </c>
@@ -7860,7 +7875,7 @@
       <c r="E117" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F117" s="333" t="s">
+      <c r="F117" s="332" t="s">
         <v>89</v>
       </c>
       <c r="G117" s="94" t="s">
@@ -7886,7 +7901,7 @@
       <c r="E118" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F118" s="334"/>
+      <c r="F118" s="333"/>
       <c r="G118" s="98" t="s">
         <v>87</v>
       </c>
@@ -9436,7 +9451,7 @@
       <c r="E180" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F180" s="333" t="s">
+      <c r="F180" s="332" t="s">
         <v>120</v>
       </c>
       <c r="G180" s="94" t="s">
@@ -9465,7 +9480,7 @@
       <c r="E181" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F181" s="348"/>
+      <c r="F181" s="347"/>
       <c r="G181" s="136" t="s">
         <v>118</v>
       </c>
@@ -9492,7 +9507,7 @@
       <c r="E182" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="F182" s="334"/>
+      <c r="F182" s="333"/>
       <c r="G182" s="98" t="s">
         <v>118</v>
       </c>
@@ -9621,7 +9636,7 @@
       <c r="E187" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F187" s="333" t="s">
+      <c r="F187" s="332" t="s">
         <v>124</v>
       </c>
       <c r="G187" s="94" t="s">
@@ -9647,7 +9662,7 @@
       <c r="E188" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F188" s="348"/>
+      <c r="F188" s="347"/>
       <c r="G188" s="136" t="s">
         <v>123</v>
       </c>
@@ -9671,7 +9686,7 @@
       <c r="E189" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F189" s="334"/>
+      <c r="F189" s="333"/>
       <c r="G189" s="98" t="s">
         <v>123</v>
       </c>
@@ -9695,7 +9710,7 @@
       <c r="E190" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F190" s="333" t="s">
+      <c r="F190" s="332" t="s">
         <v>125</v>
       </c>
       <c r="G190" s="94" t="s">
@@ -9721,7 +9736,7 @@
       <c r="E191" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F191" s="348"/>
+      <c r="F191" s="347"/>
       <c r="G191" s="136" t="s">
         <v>123</v>
       </c>
@@ -9745,7 +9760,7 @@
       <c r="E192" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F192" s="348"/>
+      <c r="F192" s="347"/>
       <c r="G192" s="136" t="s">
         <v>123</v>
       </c>
@@ -9769,7 +9784,7 @@
       <c r="E193" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F193" s="348"/>
+      <c r="F193" s="347"/>
       <c r="G193" s="136" t="s">
         <v>123</v>
       </c>
@@ -9793,7 +9808,7 @@
       <c r="E194" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F194" s="348"/>
+      <c r="F194" s="347"/>
       <c r="G194" s="136" t="s">
         <v>123</v>
       </c>
@@ -9817,7 +9832,7 @@
       <c r="E195" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F195" s="334"/>
+      <c r="F195" s="333"/>
       <c r="G195" s="98" t="s">
         <v>123</v>
       </c>
@@ -10453,7 +10468,7 @@
       <c r="E220" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F220" s="333" t="s">
+      <c r="F220" s="332" t="s">
         <v>141</v>
       </c>
       <c r="G220" s="94" t="s">
@@ -10481,7 +10496,7 @@
       <c r="E221" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F221" s="348"/>
+      <c r="F221" s="347"/>
       <c r="G221" s="136" t="s">
         <v>140</v>
       </c>
@@ -10505,7 +10520,7 @@
       <c r="E222" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="F222" s="334"/>
+      <c r="F222" s="333"/>
       <c r="G222" s="98" t="s">
         <v>140</v>
       </c>
@@ -10530,7 +10545,7 @@
       <c r="E223" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F223" s="348" t="s">
+      <c r="F223" s="347" t="s">
         <v>142</v>
       </c>
       <c r="G223" s="136" t="s">
@@ -10557,7 +10572,7 @@
       <c r="E224" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F224" s="348"/>
+      <c r="F224" s="347"/>
       <c r="G224" s="136" t="s">
         <v>140</v>
       </c>
@@ -10582,7 +10597,7 @@
       <c r="E225" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F225" s="334"/>
+      <c r="F225" s="333"/>
       <c r="G225" s="98" t="s">
         <v>140</v>
       </c>
@@ -10708,7 +10723,7 @@
       <c r="E230" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F230" s="333" t="s">
+      <c r="F230" s="332" t="s">
         <v>124</v>
       </c>
       <c r="G230" s="94" t="s">
@@ -10734,7 +10749,7 @@
       <c r="E231" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F231" s="348"/>
+      <c r="F231" s="347"/>
       <c r="G231" s="136" t="s">
         <v>145</v>
       </c>
@@ -10758,7 +10773,7 @@
       <c r="E232" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F232" s="334"/>
+      <c r="F232" s="333"/>
       <c r="G232" s="98" t="s">
         <v>145</v>
       </c>
@@ -10782,7 +10797,7 @@
       <c r="E233" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F233" s="333" t="s">
+      <c r="F233" s="332" t="s">
         <v>147</v>
       </c>
       <c r="G233" s="94" t="s">
@@ -10808,7 +10823,7 @@
       <c r="E234" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F234" s="348"/>
+      <c r="F234" s="347"/>
       <c r="G234" s="136" t="s">
         <v>146</v>
       </c>
@@ -10832,7 +10847,7 @@
       <c r="E235" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F235" s="348"/>
+      <c r="F235" s="347"/>
       <c r="G235" s="136" t="s">
         <v>146</v>
       </c>
@@ -10856,7 +10871,7 @@
       <c r="E236" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F236" s="348"/>
+      <c r="F236" s="347"/>
       <c r="G236" s="136" t="s">
         <v>146</v>
       </c>
@@ -10880,7 +10895,7 @@
       <c r="E237" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F237" s="334"/>
+      <c r="F237" s="333"/>
       <c r="G237" s="98" t="s">
         <v>146</v>
       </c>
@@ -10982,7 +10997,7 @@
       <c r="E241" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F241" s="333" t="s">
+      <c r="F241" s="332" t="s">
         <v>151</v>
       </c>
       <c r="G241" s="94" t="s">
@@ -11008,7 +11023,7 @@
       <c r="E242" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F242" s="348"/>
+      <c r="F242" s="347"/>
       <c r="G242" s="136" t="s">
         <v>150</v>
       </c>
@@ -11032,7 +11047,7 @@
       <c r="E243" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F243" s="334"/>
+      <c r="F243" s="333"/>
       <c r="G243" s="98" t="s">
         <v>150</v>
       </c>
@@ -11056,7 +11071,7 @@
       <c r="E244" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F244" s="333" t="s">
+      <c r="F244" s="332" t="s">
         <v>152</v>
       </c>
       <c r="G244" s="94" t="s">
@@ -11082,7 +11097,7 @@
       <c r="E245" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F245" s="348"/>
+      <c r="F245" s="347"/>
       <c r="G245" s="136" t="s">
         <v>153</v>
       </c>
@@ -11106,7 +11121,7 @@
       <c r="E246" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="F246" s="334"/>
+      <c r="F246" s="333"/>
       <c r="G246" s="98" t="s">
         <v>153</v>
       </c>
@@ -11208,7 +11223,7 @@
       <c r="E250" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F250" s="333" t="s">
+      <c r="F250" s="332" t="s">
         <v>157</v>
       </c>
       <c r="G250" s="94" t="s">
@@ -11234,7 +11249,7 @@
       <c r="E251" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F251" s="348"/>
+      <c r="F251" s="347"/>
       <c r="G251" s="136" t="s">
         <v>156</v>
       </c>
@@ -11258,7 +11273,7 @@
       <c r="E252" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F252" s="334"/>
+      <c r="F252" s="333"/>
       <c r="G252" s="98" t="s">
         <v>156</v>
       </c>
@@ -12141,7 +12156,7 @@
       <c r="E287" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F287" s="333" t="s">
+      <c r="F287" s="332" t="s">
         <v>174</v>
       </c>
       <c r="G287" s="94" t="s">
@@ -12167,7 +12182,7 @@
       <c r="E288" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F288" s="348"/>
+      <c r="F288" s="347"/>
       <c r="G288" s="136" t="s">
         <v>173</v>
       </c>
@@ -12191,7 +12206,7 @@
       <c r="E289" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="F289" s="334"/>
+      <c r="F289" s="333"/>
       <c r="G289" s="98" t="s">
         <v>173</v>
       </c>
@@ -12215,7 +12230,7 @@
       <c r="E290" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F290" s="348" t="s">
+      <c r="F290" s="347" t="s">
         <v>142</v>
       </c>
       <c r="G290" s="136" t="s">
@@ -12241,7 +12256,7 @@
       <c r="E291" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F291" s="334"/>
+      <c r="F291" s="333"/>
       <c r="G291" s="98" t="s">
         <v>173</v>
       </c>
@@ -12343,7 +12358,7 @@
       <c r="E295" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F295" s="333" t="s">
+      <c r="F295" s="332" t="s">
         <v>179</v>
       </c>
       <c r="G295" s="94" t="s">
@@ -12369,7 +12384,7 @@
       <c r="E296" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F296" s="348"/>
+      <c r="F296" s="347"/>
       <c r="G296" s="136" t="s">
         <v>177</v>
       </c>
@@ -12393,7 +12408,7 @@
       <c r="E297" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F297" s="334"/>
+      <c r="F297" s="333"/>
       <c r="G297" s="98" t="s">
         <v>177</v>
       </c>
@@ -12417,7 +12432,7 @@
       <c r="E298" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F298" s="333" t="s">
+      <c r="F298" s="332" t="s">
         <v>169</v>
       </c>
       <c r="G298" s="94" t="s">
@@ -12443,7 +12458,7 @@
       <c r="E299" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F299" s="348"/>
+      <c r="F299" s="347"/>
       <c r="G299" s="136" t="s">
         <v>177</v>
       </c>
@@ -12467,7 +12482,7 @@
       <c r="E300" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="F300" s="334"/>
+      <c r="F300" s="333"/>
       <c r="G300" s="98" t="s">
         <v>177</v>
       </c>
@@ -12491,7 +12506,7 @@
       <c r="E301" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F301" s="348" t="s">
+      <c r="F301" s="347" t="s">
         <v>178</v>
       </c>
       <c r="G301" s="136" t="s">
@@ -12517,7 +12532,7 @@
       <c r="E302" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F302" s="348"/>
+      <c r="F302" s="347"/>
       <c r="G302" s="144" t="s">
         <v>177</v>
       </c>
@@ -12595,7 +12610,7 @@
       <c r="E305" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F305" s="333" t="s">
+      <c r="F305" s="332" t="s">
         <v>182</v>
       </c>
       <c r="G305" s="94" t="s">
@@ -12621,7 +12636,7 @@
       <c r="E306" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F306" s="334"/>
+      <c r="F306" s="333"/>
       <c r="G306" s="98" t="s">
         <v>181</v>
       </c>
@@ -12725,7 +12740,7 @@
       <c r="E310" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F310" s="333" t="s">
+      <c r="F310" s="332" t="s">
         <v>185</v>
       </c>
       <c r="G310" s="94" t="s">
@@ -12751,7 +12766,7 @@
       <c r="E311" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F311" s="348"/>
+      <c r="F311" s="347"/>
       <c r="G311" s="136" t="s">
         <v>187</v>
       </c>
@@ -12775,7 +12790,7 @@
       <c r="E312" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F312" s="334"/>
+      <c r="F312" s="333"/>
       <c r="G312" s="98" t="s">
         <v>187</v>
       </c>
@@ -12977,7 +12992,7 @@
       <c r="E320" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F320" s="333" t="s">
+      <c r="F320" s="332" t="s">
         <v>192</v>
       </c>
       <c r="G320" s="94" t="s">
@@ -13003,7 +13018,7 @@
       <c r="E321" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F321" s="348"/>
+      <c r="F321" s="347"/>
       <c r="G321" s="136" t="s">
         <v>191</v>
       </c>
@@ -13027,7 +13042,7 @@
       <c r="E322" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="F322" s="348"/>
+      <c r="F322" s="347"/>
       <c r="G322" s="144" t="s">
         <v>191</v>
       </c>
@@ -13131,7 +13146,7 @@
       <c r="E326" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F326" s="333" t="s">
+      <c r="F326" s="332" t="s">
         <v>197</v>
       </c>
       <c r="G326" s="94" t="s">
@@ -13157,7 +13172,7 @@
       <c r="E327" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F327" s="348"/>
+      <c r="F327" s="347"/>
       <c r="G327" s="136" t="s">
         <v>196</v>
       </c>
@@ -13181,7 +13196,7 @@
       <c r="E328" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F328" s="334"/>
+      <c r="F328" s="333"/>
       <c r="G328" s="98" t="s">
         <v>196</v>
       </c>
@@ -13364,7 +13379,7 @@
       <c r="E335" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F335" s="333" t="s">
+      <c r="F335" s="332" t="s">
         <v>201</v>
       </c>
       <c r="G335" s="94" t="s">
@@ -13390,7 +13405,7 @@
       <c r="E336" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F336" s="348"/>
+      <c r="F336" s="347"/>
       <c r="G336" s="136" t="s">
         <v>200</v>
       </c>
@@ -13414,7 +13429,7 @@
       <c r="E337" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F337" s="334"/>
+      <c r="F337" s="333"/>
       <c r="G337" s="98" t="s">
         <v>200</v>
       </c>
@@ -13516,13 +13531,13 @@
       <c r="E341" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F341" s="333" t="s">
+      <c r="F341" s="332" t="s">
         <v>151</v>
       </c>
       <c r="G341" s="194" t="s">
         <v>205</v>
       </c>
-      <c r="H341" s="331" t="s">
+      <c r="H341" s="330" t="s">
         <v>63</v>
       </c>
       <c r="I341" s="183" t="str">
@@ -13544,11 +13559,11 @@
       <c r="E342" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F342" s="348"/>
+      <c r="F342" s="347"/>
       <c r="G342" s="195" t="s">
         <v>205</v>
       </c>
-      <c r="H342" s="344"/>
+      <c r="H342" s="343"/>
       <c r="I342" s="184" t="str">
         <f t="shared" si="4"/>
         <v>10,24</v>
@@ -13568,11 +13583,11 @@
       <c r="E343" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="F343" s="334"/>
+      <c r="F343" s="333"/>
       <c r="G343" s="196" t="s">
         <v>205</v>
       </c>
-      <c r="H343" s="344"/>
+      <c r="H343" s="343"/>
       <c r="I343" s="182" t="str">
         <f t="shared" si="4"/>
         <v>10,24</v>
@@ -13592,13 +13607,13 @@
       <c r="E344" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="F344" s="333" t="s">
+      <c r="F344" s="332" t="s">
         <v>202</v>
       </c>
       <c r="G344" s="194" t="s">
         <v>205</v>
       </c>
-      <c r="H344" s="344"/>
+      <c r="H344" s="343"/>
       <c r="I344" s="183" t="str">
         <f t="shared" si="4"/>
         <v>10,24</v>
@@ -13618,11 +13633,11 @@
       <c r="E345" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F345" s="348"/>
+      <c r="F345" s="347"/>
       <c r="G345" s="195" t="s">
         <v>205</v>
       </c>
-      <c r="H345" s="344"/>
+      <c r="H345" s="343"/>
       <c r="I345" s="184" t="str">
         <f t="shared" si="4"/>
         <v>10,24</v>
@@ -13642,11 +13657,11 @@
       <c r="E346" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F346" s="334"/>
+      <c r="F346" s="333"/>
       <c r="G346" s="196" t="s">
         <v>205</v>
       </c>
-      <c r="H346" s="332"/>
+      <c r="H346" s="331"/>
       <c r="I346" s="182" t="str">
         <f t="shared" si="4"/>
         <v>10,24</v>
@@ -14044,7 +14059,7 @@
       <c r="E362" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F362" s="333" t="s">
+      <c r="F362" s="332" t="s">
         <v>68</v>
       </c>
       <c r="G362" s="94" t="s">
@@ -14070,7 +14085,7 @@
       <c r="E363" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F363" s="348"/>
+      <c r="F363" s="347"/>
       <c r="G363" s="136" t="s">
         <v>210</v>
       </c>
@@ -14094,7 +14109,7 @@
       <c r="E364" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F364" s="334"/>
+      <c r="F364" s="333"/>
       <c r="G364" s="98" t="s">
         <v>210</v>
       </c>
@@ -14119,7 +14134,7 @@
       <c r="E365" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F365" s="333" t="s">
+      <c r="F365" s="332" t="s">
         <v>211</v>
       </c>
       <c r="G365" s="136" t="s">
@@ -14146,7 +14161,7 @@
       <c r="E366" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F366" s="348"/>
+      <c r="F366" s="347"/>
       <c r="G366" s="136" t="s">
         <v>210</v>
       </c>
@@ -14171,7 +14186,7 @@
       <c r="E367" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F367" s="348"/>
+      <c r="F367" s="347"/>
       <c r="G367" s="136" t="s">
         <v>210</v>
       </c>
@@ -14196,7 +14211,7 @@
       <c r="E368" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F368" s="348"/>
+      <c r="F368" s="347"/>
       <c r="G368" s="136" t="s">
         <v>210</v>
       </c>
@@ -14220,7 +14235,7 @@
       <c r="E369" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F369" s="348"/>
+      <c r="F369" s="347"/>
       <c r="G369" s="136" t="s">
         <v>210</v>
       </c>
@@ -14244,7 +14259,7 @@
       <c r="E370" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F370" s="348"/>
+      <c r="F370" s="347"/>
       <c r="G370" s="136" t="s">
         <v>210</v>
       </c>
@@ -14268,7 +14283,7 @@
       <c r="E371" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F371" s="334"/>
+      <c r="F371" s="333"/>
       <c r="G371" s="98" t="s">
         <v>210</v>
       </c>
@@ -14372,7 +14387,7 @@
       <c r="E375" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F375" s="333" t="s">
+      <c r="F375" s="332" t="s">
         <v>108</v>
       </c>
       <c r="G375" s="136" t="s">
@@ -14398,7 +14413,7 @@
       <c r="E376" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F376" s="348"/>
+      <c r="F376" s="347"/>
       <c r="G376" s="136" t="s">
         <v>215</v>
       </c>
@@ -14422,7 +14437,7 @@
       <c r="E377" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F377" s="334"/>
+      <c r="F377" s="333"/>
       <c r="G377" s="98" t="s">
         <v>215</v>
       </c>
@@ -14446,7 +14461,7 @@
       <c r="E378" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F378" s="333" t="s">
+      <c r="F378" s="332" t="s">
         <v>216</v>
       </c>
       <c r="G378" s="136" t="s">
@@ -14472,7 +14487,7 @@
       <c r="E379" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F379" s="348"/>
+      <c r="F379" s="347"/>
       <c r="G379" s="136" t="s">
         <v>215</v>
       </c>
@@ -14496,7 +14511,7 @@
       <c r="E380" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F380" s="348"/>
+      <c r="F380" s="347"/>
       <c r="G380" s="136" t="s">
         <v>215</v>
       </c>
@@ -14520,7 +14535,7 @@
       <c r="E381" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F381" s="348"/>
+      <c r="F381" s="347"/>
       <c r="G381" s="136" t="s">
         <v>215</v>
       </c>
@@ -14544,7 +14559,7 @@
       <c r="E382" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F382" s="348"/>
+      <c r="F382" s="347"/>
       <c r="G382" s="136" t="s">
         <v>215</v>
       </c>
@@ -14568,7 +14583,7 @@
       <c r="E383" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F383" s="348"/>
+      <c r="F383" s="347"/>
       <c r="G383" s="136" t="s">
         <v>215</v>
       </c>
@@ -14592,7 +14607,7 @@
       <c r="E384" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F384" s="348"/>
+      <c r="F384" s="347"/>
       <c r="G384" s="144" t="s">
         <v>215</v>
       </c>
@@ -15044,7 +15059,7 @@
       <c r="E402" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F402" s="333" t="s">
+      <c r="F402" s="332" t="s">
         <v>225</v>
       </c>
       <c r="G402" s="94" t="s">
@@ -15070,7 +15085,7 @@
       <c r="E403" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F403" s="348"/>
+      <c r="F403" s="347"/>
       <c r="G403" s="136" t="s">
         <v>224</v>
       </c>
@@ -15094,7 +15109,7 @@
       <c r="E404" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F404" s="348"/>
+      <c r="F404" s="347"/>
       <c r="G404" s="136" t="s">
         <v>224</v>
       </c>
@@ -15118,7 +15133,7 @@
       <c r="E405" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F405" s="334"/>
+      <c r="F405" s="333"/>
       <c r="G405" s="98" t="s">
         <v>224</v>
       </c>
@@ -15392,7 +15407,7 @@
       <c r="E416" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F416" s="333" t="s">
+      <c r="F416" s="332" t="s">
         <v>230</v>
       </c>
       <c r="G416" s="94" t="s">
@@ -15418,7 +15433,7 @@
       <c r="E417" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F417" s="348"/>
+      <c r="F417" s="347"/>
       <c r="G417" s="136" t="s">
         <v>229</v>
       </c>
@@ -15442,7 +15457,7 @@
       <c r="E418" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F418" s="334"/>
+      <c r="F418" s="333"/>
       <c r="G418" s="98" t="s">
         <v>229</v>
       </c>
@@ -15716,7 +15731,7 @@
       <c r="E429" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F429" s="333" t="s">
+      <c r="F429" s="332" t="s">
         <v>235</v>
       </c>
       <c r="G429" s="94" t="s">
@@ -15742,7 +15757,7 @@
       <c r="E430" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F430" s="348"/>
+      <c r="F430" s="347"/>
       <c r="G430" s="136" t="s">
         <v>234</v>
       </c>
@@ -15766,7 +15781,7 @@
       <c r="E431" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F431" s="348"/>
+      <c r="F431" s="347"/>
       <c r="G431" s="136" t="s">
         <v>234</v>
       </c>
@@ -15790,7 +15805,7 @@
       <c r="E432" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F432" s="334"/>
+      <c r="F432" s="333"/>
       <c r="G432" s="98" t="s">
         <v>234</v>
       </c>
@@ -16386,7 +16401,7 @@
       <c r="E456" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F456" s="333" t="s">
+      <c r="F456" s="332" t="s">
         <v>244</v>
       </c>
       <c r="G456" s="94" t="s">
@@ -16412,7 +16427,7 @@
       <c r="E457" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F457" s="348"/>
+      <c r="F457" s="347"/>
       <c r="G457" s="136" t="s">
         <v>243</v>
       </c>
@@ -16436,7 +16451,7 @@
       <c r="E458" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F458" s="348"/>
+      <c r="F458" s="347"/>
       <c r="G458" s="136" t="s">
         <v>243</v>
       </c>
@@ -16460,7 +16475,7 @@
       <c r="E459" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F459" s="334"/>
+      <c r="F459" s="333"/>
       <c r="G459" s="98" t="s">
         <v>243</v>
       </c>
@@ -16910,7 +16925,7 @@
       <c r="E477" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F477" s="333" t="s">
+      <c r="F477" s="332" t="s">
         <v>252</v>
       </c>
       <c r="G477" s="94" t="s">
@@ -16936,7 +16951,7 @@
       <c r="E478" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F478" s="348"/>
+      <c r="F478" s="347"/>
       <c r="G478" s="136" t="s">
         <v>251</v>
       </c>
@@ -16960,7 +16975,7 @@
       <c r="E479" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F479" s="348"/>
+      <c r="F479" s="347"/>
       <c r="G479" s="136" t="s">
         <v>251</v>
       </c>
@@ -16984,7 +16999,7 @@
       <c r="E480" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F480" s="348"/>
+      <c r="F480" s="347"/>
       <c r="G480" s="136" t="s">
         <v>251</v>
       </c>
@@ -17008,7 +17023,7 @@
       <c r="E481" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F481" s="348"/>
+      <c r="F481" s="347"/>
       <c r="G481" s="136" t="s">
         <v>251</v>
       </c>
@@ -17032,7 +17047,7 @@
       <c r="E482" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F482" s="348"/>
+      <c r="F482" s="347"/>
       <c r="G482" s="144" t="s">
         <v>251</v>
       </c>
@@ -17384,7 +17399,7 @@
       <c r="E496" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F496" s="333" t="s">
+      <c r="F496" s="332" t="s">
         <v>260</v>
       </c>
       <c r="G496" s="94" t="s">
@@ -17410,7 +17425,7 @@
       <c r="E497" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F497" s="348"/>
+      <c r="F497" s="347"/>
       <c r="G497" s="136" t="s">
         <v>259</v>
       </c>
@@ -17434,7 +17449,7 @@
       <c r="E498" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F498" s="334"/>
+      <c r="F498" s="333"/>
       <c r="G498" s="98" t="s">
         <v>259</v>
       </c>
@@ -17560,7 +17575,7 @@
       <c r="E503" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F503" s="333" t="s">
+      <c r="F503" s="332" t="s">
         <v>262</v>
       </c>
       <c r="G503" s="94" t="s">
@@ -17586,7 +17601,7 @@
       <c r="E504" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F504" s="348"/>
+      <c r="F504" s="347"/>
       <c r="G504" s="136" t="s">
         <v>261</v>
       </c>
@@ -17610,7 +17625,7 @@
       <c r="E505" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F505" s="348"/>
+      <c r="F505" s="347"/>
       <c r="G505" s="136" t="s">
         <v>261</v>
       </c>
@@ -17634,7 +17649,7 @@
       <c r="E506" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F506" s="348"/>
+      <c r="F506" s="347"/>
       <c r="G506" s="136" t="s">
         <v>261</v>
       </c>
@@ -17658,7 +17673,7 @@
       <c r="E507" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F507" s="348"/>
+      <c r="F507" s="347"/>
       <c r="G507" s="136" t="s">
         <v>261</v>
       </c>
@@ -17682,7 +17697,7 @@
       <c r="E508" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F508" s="348"/>
+      <c r="F508" s="347"/>
       <c r="G508" s="136" t="s">
         <v>261</v>
       </c>
@@ -17706,7 +17721,7 @@
       <c r="E509" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F509" s="334"/>
+      <c r="F509" s="333"/>
       <c r="G509" s="98" t="s">
         <v>261</v>
       </c>
@@ -17834,7 +17849,7 @@
       <c r="E514" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F514" s="333" t="s">
+      <c r="F514" s="332" t="s">
         <v>124</v>
       </c>
       <c r="G514" s="94" t="s">
@@ -17860,7 +17875,7 @@
       <c r="E515" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F515" s="348"/>
+      <c r="F515" s="347"/>
       <c r="G515" s="136" t="s">
         <v>265</v>
       </c>
@@ -17884,7 +17899,7 @@
       <c r="E516" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F516" s="334"/>
+      <c r="F516" s="333"/>
       <c r="G516" s="98" t="s">
         <v>265</v>
       </c>
@@ -17908,7 +17923,7 @@
       <c r="E517" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F517" s="348" t="s">
+      <c r="F517" s="347" t="s">
         <v>266</v>
       </c>
       <c r="G517" s="136" t="s">
@@ -17934,7 +17949,7 @@
       <c r="E518" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F518" s="348"/>
+      <c r="F518" s="347"/>
       <c r="G518" s="136" t="s">
         <v>265</v>
       </c>
@@ -17958,7 +17973,7 @@
       <c r="E519" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F519" s="348"/>
+      <c r="F519" s="347"/>
       <c r="G519" s="136" t="s">
         <v>265</v>
       </c>
@@ -17982,7 +17997,7 @@
       <c r="E520" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F520" s="334"/>
+      <c r="F520" s="333"/>
       <c r="G520" s="98" t="s">
         <v>265</v>
       </c>
@@ -18110,7 +18125,7 @@
       <c r="E525" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F525" s="333" t="s">
+      <c r="F525" s="332" t="s">
         <v>270</v>
       </c>
       <c r="G525" s="94" t="s">
@@ -18136,7 +18151,7 @@
       <c r="E526" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F526" s="348"/>
+      <c r="F526" s="347"/>
       <c r="G526" s="136" t="s">
         <v>269</v>
       </c>
@@ -18160,7 +18175,7 @@
       <c r="E527" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F527" s="334"/>
+      <c r="F527" s="333"/>
       <c r="G527" s="98" t="s">
         <v>269</v>
       </c>
@@ -18184,7 +18199,7 @@
       <c r="E528" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F528" s="348" t="s">
+      <c r="F528" s="347" t="s">
         <v>271</v>
       </c>
       <c r="G528" s="136" t="s">
@@ -18210,7 +18225,7 @@
       <c r="E529" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F529" s="348"/>
+      <c r="F529" s="347"/>
       <c r="G529" s="136" t="s">
         <v>269</v>
       </c>
@@ -18234,7 +18249,7 @@
       <c r="E530" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F530" s="348"/>
+      <c r="F530" s="347"/>
       <c r="G530" s="136" t="s">
         <v>269</v>
       </c>
@@ -18258,7 +18273,7 @@
       <c r="E531" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F531" s="348"/>
+      <c r="F531" s="347"/>
       <c r="G531" s="136" t="s">
         <v>269</v>
       </c>
@@ -18282,7 +18297,7 @@
       <c r="E532" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F532" s="334"/>
+      <c r="F532" s="333"/>
       <c r="G532" s="98" t="s">
         <v>269</v>
       </c>
@@ -18410,7 +18425,7 @@
       <c r="E537" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F537" s="333" t="s">
+      <c r="F537" s="332" t="s">
         <v>94</v>
       </c>
       <c r="G537" s="94" t="s">
@@ -18436,7 +18451,7 @@
       <c r="E538" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F538" s="348"/>
+      <c r="F538" s="347"/>
       <c r="G538" s="136" t="s">
         <v>274</v>
       </c>
@@ -18460,7 +18475,7 @@
       <c r="E539" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F539" s="334"/>
+      <c r="F539" s="333"/>
       <c r="G539" s="98" t="s">
         <v>274</v>
       </c>
@@ -18484,7 +18499,7 @@
       <c r="E540" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F540" s="348" t="s">
+      <c r="F540" s="347" t="s">
         <v>102</v>
       </c>
       <c r="G540" s="136" t="s">
@@ -18510,7 +18525,7 @@
       <c r="E541" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F541" s="348"/>
+      <c r="F541" s="347"/>
       <c r="G541" s="136" t="s">
         <v>274</v>
       </c>
@@ -18534,7 +18549,7 @@
       <c r="E542" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F542" s="348"/>
+      <c r="F542" s="347"/>
       <c r="G542" s="136" t="s">
         <v>274</v>
       </c>
@@ -18558,7 +18573,7 @@
       <c r="E543" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F543" s="348"/>
+      <c r="F543" s="347"/>
       <c r="G543" s="136" t="s">
         <v>274</v>
       </c>
@@ -18582,7 +18597,7 @@
       <c r="E544" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F544" s="348"/>
+      <c r="F544" s="347"/>
       <c r="G544" s="144" t="s">
         <v>274</v>
       </c>
@@ -19032,7 +19047,7 @@
       <c r="E562" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F562" s="333" t="s">
+      <c r="F562" s="332" t="s">
         <v>285</v>
       </c>
       <c r="G562" s="94" t="s">
@@ -19058,7 +19073,7 @@
       <c r="E563" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F563" s="348"/>
+      <c r="F563" s="347"/>
       <c r="G563" s="136" t="s">
         <v>284</v>
       </c>
@@ -19082,7 +19097,7 @@
       <c r="E564" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F564" s="334"/>
+      <c r="F564" s="333"/>
       <c r="G564" s="98" t="s">
         <v>284</v>
       </c>
@@ -19359,7 +19374,7 @@
       <c r="E575" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F575" s="333" t="s">
+      <c r="F575" s="332" t="s">
         <v>292</v>
       </c>
       <c r="G575" s="94" t="s">
@@ -19385,7 +19400,7 @@
       <c r="E576" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F576" s="348"/>
+      <c r="F576" s="347"/>
       <c r="G576" s="136" t="s">
         <v>291</v>
       </c>
@@ -19409,7 +19424,7 @@
       <c r="E577" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F577" s="348"/>
+      <c r="F577" s="347"/>
       <c r="G577" s="136" t="s">
         <v>291</v>
       </c>
@@ -19433,7 +19448,7 @@
       <c r="E578" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F578" s="334"/>
+      <c r="F578" s="333"/>
       <c r="G578" s="98" t="s">
         <v>291</v>
       </c>
@@ -19731,7 +19746,7 @@
       <c r="E590" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F590" s="333" t="s">
+      <c r="F590" s="332" t="s">
         <v>297</v>
       </c>
       <c r="G590" s="94" t="s">
@@ -19757,7 +19772,7 @@
       <c r="E591" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F591" s="348"/>
+      <c r="F591" s="347"/>
       <c r="G591" s="136" t="s">
         <v>296</v>
       </c>
@@ -19781,7 +19796,7 @@
       <c r="E592" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F592" s="334"/>
+      <c r="F592" s="333"/>
       <c r="G592" s="98" t="s">
         <v>296</v>
       </c>
@@ -20055,7 +20070,7 @@
       <c r="E603" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F603" s="333" t="s">
+      <c r="F603" s="332" t="s">
         <v>304</v>
       </c>
       <c r="G603" s="94" t="s">
@@ -20081,7 +20096,7 @@
       <c r="E604" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F604" s="348"/>
+      <c r="F604" s="347"/>
       <c r="G604" s="136" t="s">
         <v>303</v>
       </c>
@@ -20105,7 +20120,7 @@
       <c r="E605" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F605" s="348"/>
+      <c r="F605" s="347"/>
       <c r="G605" s="136" t="s">
         <v>303</v>
       </c>
@@ -20129,7 +20144,7 @@
       <c r="E606" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F606" s="348"/>
+      <c r="F606" s="347"/>
       <c r="G606" s="136" t="s">
         <v>303</v>
       </c>
@@ -20153,7 +20168,7 @@
       <c r="E607" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F607" s="334"/>
+      <c r="F607" s="333"/>
       <c r="G607" s="98" t="s">
         <v>303</v>
       </c>
@@ -20281,7 +20296,7 @@
       <c r="E612" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F612" s="333" t="s">
+      <c r="F612" s="332" t="s">
         <v>309</v>
       </c>
       <c r="G612" s="94" t="s">
@@ -20307,7 +20322,7 @@
       <c r="E613" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F613" s="348"/>
+      <c r="F613" s="347"/>
       <c r="G613" s="136" t="s">
         <v>308</v>
       </c>
@@ -20331,7 +20346,7 @@
       <c r="E614" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F614" s="348"/>
+      <c r="F614" s="347"/>
       <c r="G614" s="136" t="s">
         <v>308</v>
       </c>
@@ -20355,7 +20370,7 @@
       <c r="E615" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F615" s="334"/>
+      <c r="F615" s="333"/>
       <c r="G615" s="98" t="s">
         <v>308</v>
       </c>
@@ -20507,7 +20522,7 @@
       <c r="E621" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F621" s="333" t="s">
+      <c r="F621" s="332" t="s">
         <v>312</v>
       </c>
       <c r="G621" s="94" t="s">
@@ -20533,7 +20548,7 @@
       <c r="E622" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F622" s="348"/>
+      <c r="F622" s="347"/>
       <c r="G622" s="136" t="s">
         <v>310</v>
       </c>
@@ -20557,7 +20572,7 @@
       <c r="E623" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F623" s="348"/>
+      <c r="F623" s="347"/>
       <c r="G623" s="136" t="s">
         <v>310</v>
       </c>
@@ -20581,7 +20596,7 @@
       <c r="E624" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F624" s="348"/>
+      <c r="F624" s="347"/>
       <c r="G624" s="136" t="s">
         <v>310</v>
       </c>
@@ -20605,7 +20620,7 @@
       <c r="E625" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F625" s="348"/>
+      <c r="F625" s="347"/>
       <c r="G625" s="136" t="s">
         <v>310</v>
       </c>
@@ -20629,7 +20644,7 @@
       <c r="E626" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F626" s="348"/>
+      <c r="F626" s="347"/>
       <c r="G626" s="136" t="s">
         <v>310</v>
       </c>
@@ -20653,7 +20668,7 @@
       <c r="E627" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F627" s="334"/>
+      <c r="F627" s="333"/>
       <c r="G627" s="98" t="s">
         <v>310</v>
       </c>
@@ -20781,7 +20796,7 @@
       <c r="E632" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F632" s="333" t="s">
+      <c r="F632" s="332" t="s">
         <v>317</v>
       </c>
       <c r="G632" s="94" t="s">
@@ -20807,7 +20822,7 @@
       <c r="E633" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F633" s="348"/>
+      <c r="F633" s="347"/>
       <c r="G633" s="136" t="s">
         <v>316</v>
       </c>
@@ -20831,7 +20846,7 @@
       <c r="E634" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F634" s="348"/>
+      <c r="F634" s="347"/>
       <c r="G634" s="136" t="s">
         <v>316</v>
       </c>
@@ -20855,7 +20870,7 @@
       <c r="E635" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F635" s="348"/>
+      <c r="F635" s="347"/>
       <c r="G635" s="136" t="s">
         <v>316</v>
       </c>
@@ -20879,7 +20894,7 @@
       <c r="E636" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F636" s="334"/>
+      <c r="F636" s="333"/>
       <c r="G636" s="98" t="s">
         <v>316</v>
       </c>
@@ -20903,7 +20918,7 @@
       <c r="E637" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F637" s="348" t="s">
+      <c r="F637" s="347" t="s">
         <v>318</v>
       </c>
       <c r="G637" s="136" t="s">
@@ -20929,7 +20944,7 @@
       <c r="E638" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F638" s="348"/>
+      <c r="F638" s="347"/>
       <c r="G638" s="136" t="s">
         <v>316</v>
       </c>
@@ -20953,7 +20968,7 @@
       <c r="E639" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F639" s="348"/>
+      <c r="F639" s="347"/>
       <c r="G639" s="136" t="s">
         <v>316</v>
       </c>
@@ -20977,7 +20992,7 @@
       <c r="E640" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="F640" s="348"/>
+      <c r="F640" s="347"/>
       <c r="G640" s="144" t="s">
         <v>316</v>
       </c>
@@ -21131,7 +21146,7 @@
       <c r="E646" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F646" s="333" t="s">
+      <c r="F646" s="332" t="s">
         <v>311</v>
       </c>
       <c r="G646" s="94" t="s">
@@ -21157,7 +21172,7 @@
       <c r="E647" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F647" s="348"/>
+      <c r="F647" s="347"/>
       <c r="G647" s="136" t="s">
         <v>324</v>
       </c>
@@ -21181,7 +21196,7 @@
       <c r="E648" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F648" s="348"/>
+      <c r="F648" s="347"/>
       <c r="G648" s="136" t="s">
         <v>324</v>
       </c>
@@ -21205,7 +21220,7 @@
       <c r="E649" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F649" s="334"/>
+      <c r="F649" s="333"/>
       <c r="G649" s="98" t="s">
         <v>324</v>
       </c>
@@ -21381,7 +21396,7 @@
       <c r="E656" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F656" s="333" t="s">
+      <c r="F656" s="332" t="s">
         <v>328</v>
       </c>
       <c r="G656" s="94" t="s">
@@ -21407,7 +21422,7 @@
       <c r="E657" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F657" s="348"/>
+      <c r="F657" s="347"/>
       <c r="G657" s="136" t="s">
         <v>327</v>
       </c>
@@ -21431,7 +21446,7 @@
       <c r="E658" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F658" s="348"/>
+      <c r="F658" s="347"/>
       <c r="G658" s="136" t="s">
         <v>327</v>
       </c>
@@ -21455,7 +21470,7 @@
       <c r="E659" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F659" s="334"/>
+      <c r="F659" s="333"/>
       <c r="G659" s="98" t="s">
         <v>327</v>
       </c>
@@ -21607,7 +21622,7 @@
       <c r="E665" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F665" s="333" t="s">
+      <c r="F665" s="332" t="s">
         <v>332</v>
       </c>
       <c r="G665" s="94" t="s">
@@ -21633,7 +21648,7 @@
       <c r="E666" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F666" s="334"/>
+      <c r="F666" s="333"/>
       <c r="G666" s="98" t="s">
         <v>329</v>
       </c>
@@ -21657,7 +21672,7 @@
       <c r="E667" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F667" s="348" t="s">
+      <c r="F667" s="347" t="s">
         <v>331</v>
       </c>
       <c r="G667" s="136" t="s">
@@ -21683,7 +21698,7 @@
       <c r="E668" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F668" s="348"/>
+      <c r="F668" s="347"/>
       <c r="G668" s="136" t="s">
         <v>329</v>
       </c>
@@ -21707,7 +21722,7 @@
       <c r="E669" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F669" s="348"/>
+      <c r="F669" s="347"/>
       <c r="G669" s="136" t="s">
         <v>329</v>
       </c>
@@ -21731,7 +21746,7 @@
       <c r="E670" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F670" s="348"/>
+      <c r="F670" s="347"/>
       <c r="G670" s="136" t="s">
         <v>329</v>
       </c>
@@ -21755,7 +21770,7 @@
       <c r="E671" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F671" s="348"/>
+      <c r="F671" s="347"/>
       <c r="G671" s="136" t="s">
         <v>329</v>
       </c>
@@ -21779,7 +21794,7 @@
       <c r="E672" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F672" s="334"/>
+      <c r="F672" s="333"/>
       <c r="G672" s="98" t="s">
         <v>329</v>
       </c>
@@ -21929,7 +21944,7 @@
       <c r="E678" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F678" s="333" t="s">
+      <c r="F678" s="332" t="s">
         <v>335</v>
       </c>
       <c r="G678" s="94" t="s">
@@ -21955,7 +21970,7 @@
       <c r="E679" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F679" s="348"/>
+      <c r="F679" s="347"/>
       <c r="G679" s="136" t="s">
         <v>336</v>
       </c>
@@ -21979,7 +21994,7 @@
       <c r="E680" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F680" s="334"/>
+      <c r="F680" s="333"/>
       <c r="G680" s="98" t="s">
         <v>336</v>
       </c>
@@ -22003,7 +22018,7 @@
       <c r="E681" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F681" s="348" t="s">
+      <c r="F681" s="347" t="s">
         <v>337</v>
       </c>
       <c r="G681" s="136" t="s">
@@ -22029,7 +22044,7 @@
       <c r="E682" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F682" s="348"/>
+      <c r="F682" s="347"/>
       <c r="G682" s="136" t="s">
         <v>336</v>
       </c>
@@ -22053,7 +22068,7 @@
       <c r="E683" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F683" s="348"/>
+      <c r="F683" s="347"/>
       <c r="G683" s="136" t="s">
         <v>336</v>
       </c>
@@ -22077,7 +22092,7 @@
       <c r="E684" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F684" s="348"/>
+      <c r="F684" s="347"/>
       <c r="G684" s="136" t="s">
         <v>336</v>
       </c>
@@ -22101,7 +22116,7 @@
       <c r="E685" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F685" s="334"/>
+      <c r="F685" s="333"/>
       <c r="G685" s="98" t="s">
         <v>336</v>
       </c>
@@ -22359,7 +22374,7 @@
       <c r="E695" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F695" s="333" t="s">
+      <c r="F695" s="332" t="s">
         <v>346</v>
       </c>
       <c r="G695" s="94" t="s">
@@ -22385,7 +22400,7 @@
       <c r="E696" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F696" s="348"/>
+      <c r="F696" s="347"/>
       <c r="G696" s="136" t="s">
         <v>345</v>
       </c>
@@ -22409,7 +22424,7 @@
       <c r="E697" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="F697" s="348"/>
+      <c r="F697" s="347"/>
       <c r="G697" s="144" t="s">
         <v>345</v>
       </c>
@@ -22809,7 +22824,7 @@
       <c r="E713" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F713" s="333" t="s">
+      <c r="F713" s="332" t="s">
         <v>353</v>
       </c>
       <c r="G713" s="94" t="s">
@@ -22835,7 +22850,7 @@
       <c r="E714" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F714" s="348"/>
+      <c r="F714" s="347"/>
       <c r="G714" s="136" t="s">
         <v>352</v>
       </c>
@@ -22859,7 +22874,7 @@
       <c r="E715" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F715" s="348"/>
+      <c r="F715" s="347"/>
       <c r="G715" s="136" t="s">
         <v>352</v>
       </c>
@@ -22883,7 +22898,7 @@
       <c r="E716" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F716" s="334"/>
+      <c r="F716" s="333"/>
       <c r="G716" s="98" t="s">
         <v>352</v>
       </c>
@@ -23011,7 +23026,7 @@
       <c r="E721" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F721" s="333" t="s">
+      <c r="F721" s="332" t="s">
         <v>356</v>
       </c>
       <c r="G721" s="94" t="s">
@@ -23037,7 +23052,7 @@
       <c r="E722" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F722" s="348"/>
+      <c r="F722" s="347"/>
       <c r="G722" s="136" t="s">
         <v>354</v>
       </c>
@@ -23061,7 +23076,7 @@
       <c r="E723" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F723" s="334"/>
+      <c r="F723" s="333"/>
       <c r="G723" s="98" t="s">
         <v>354</v>
       </c>
@@ -23085,7 +23100,7 @@
       <c r="E724" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F724" s="333" t="s">
+      <c r="F724" s="332" t="s">
         <v>357</v>
       </c>
       <c r="G724" s="94" t="s">
@@ -23111,7 +23126,7 @@
       <c r="E725" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F725" s="348"/>
+      <c r="F725" s="347"/>
       <c r="G725" s="136" t="s">
         <v>354</v>
       </c>
@@ -23135,7 +23150,7 @@
       <c r="E726" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F726" s="348"/>
+      <c r="F726" s="347"/>
       <c r="G726" s="136" t="s">
         <v>354</v>
       </c>
@@ -23159,7 +23174,7 @@
       <c r="E727" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F727" s="348"/>
+      <c r="F727" s="347"/>
       <c r="G727" s="136" t="s">
         <v>354</v>
       </c>
@@ -23183,7 +23198,7 @@
       <c r="E728" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F728" s="348"/>
+      <c r="F728" s="347"/>
       <c r="G728" s="136" t="s">
         <v>354</v>
       </c>
@@ -23207,7 +23222,7 @@
       <c r="E729" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F729" s="348"/>
+      <c r="F729" s="347"/>
       <c r="G729" s="144" t="s">
         <v>354</v>
       </c>
@@ -23335,7 +23350,7 @@
       <c r="E734" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F734" s="333" t="s">
+      <c r="F734" s="332" t="s">
         <v>361</v>
       </c>
       <c r="G734" s="94" t="s">
@@ -23361,7 +23376,7 @@
       <c r="E735" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F735" s="348"/>
+      <c r="F735" s="347"/>
       <c r="G735" s="136" t="s">
         <v>360</v>
       </c>
@@ -23385,7 +23400,7 @@
       <c r="E736" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F736" s="348"/>
+      <c r="F736" s="347"/>
       <c r="G736" s="136" t="s">
         <v>360</v>
       </c>
@@ -23409,7 +23424,7 @@
       <c r="E737" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F737" s="334"/>
+      <c r="F737" s="333"/>
       <c r="G737" s="98" t="s">
         <v>360</v>
       </c>
@@ -23563,7 +23578,7 @@
       <c r="E743" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F743" s="333" t="s">
+      <c r="F743" s="332" t="s">
         <v>275</v>
       </c>
       <c r="G743" s="94" t="s">
@@ -23589,7 +23604,7 @@
       <c r="E744" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F744" s="348"/>
+      <c r="F744" s="347"/>
       <c r="G744" s="136" t="s">
         <v>364</v>
       </c>
@@ -23613,7 +23628,7 @@
       <c r="E745" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F745" s="348"/>
+      <c r="F745" s="347"/>
       <c r="G745" s="136" t="s">
         <v>364</v>
       </c>
@@ -23637,7 +23652,7 @@
       <c r="E746" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="F746" s="348"/>
+      <c r="F746" s="347"/>
       <c r="G746" s="144" t="s">
         <v>364</v>
       </c>
@@ -23789,7 +23804,7 @@
       <c r="E752" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F752" s="333" t="s">
+      <c r="F752" s="332" t="s">
         <v>373</v>
       </c>
       <c r="G752" s="94" t="s">
@@ -23815,7 +23830,7 @@
       <c r="E753" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F753" s="348"/>
+      <c r="F753" s="347"/>
       <c r="G753" s="136" t="s">
         <v>370</v>
       </c>
@@ -23839,7 +23854,7 @@
       <c r="E754" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F754" s="348"/>
+      <c r="F754" s="347"/>
       <c r="G754" s="136" t="s">
         <v>370</v>
       </c>
@@ -23863,7 +23878,7 @@
       <c r="E755" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F755" s="334"/>
+      <c r="F755" s="333"/>
       <c r="G755" s="98" t="s">
         <v>370</v>
       </c>
@@ -24365,7 +24380,7 @@
       <c r="E775" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F775" s="333" t="s">
+      <c r="F775" s="332" t="s">
         <v>309</v>
       </c>
       <c r="G775" s="94" t="s">
@@ -24391,7 +24406,7 @@
       <c r="E776" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F776" s="348"/>
+      <c r="F776" s="347"/>
       <c r="G776" s="136" t="s">
         <v>378</v>
       </c>
@@ -24415,7 +24430,7 @@
       <c r="E777" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F777" s="348"/>
+      <c r="F777" s="347"/>
       <c r="G777" s="136" t="s">
         <v>378</v>
       </c>
@@ -24439,7 +24454,7 @@
       <c r="E778" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F778" s="334"/>
+      <c r="F778" s="333"/>
       <c r="G778" s="98" t="s">
         <v>378</v>
       </c>
@@ -24541,7 +24556,7 @@
       <c r="E782" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F782" s="333" t="s">
+      <c r="F782" s="332" t="s">
         <v>380</v>
       </c>
       <c r="G782" s="94" t="s">
@@ -24567,7 +24582,7 @@
       <c r="E783" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F783" s="348"/>
+      <c r="F783" s="347"/>
       <c r="G783" s="136" t="s">
         <v>379</v>
       </c>
@@ -24591,7 +24606,7 @@
       <c r="E784" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F784" s="348"/>
+      <c r="F784" s="347"/>
       <c r="G784" s="136" t="s">
         <v>379</v>
       </c>
@@ -24665,7 +24680,7 @@
       <c r="E787" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F787" s="348"/>
+      <c r="F787" s="347"/>
       <c r="G787" s="136" t="s">
         <v>379</v>
       </c>
@@ -24689,7 +24704,7 @@
       <c r="E788" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F788" s="348"/>
+      <c r="F788" s="347"/>
       <c r="G788" s="136" t="s">
         <v>379</v>
       </c>
@@ -24713,7 +24728,7 @@
       <c r="E789" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F789" s="334"/>
+      <c r="F789" s="333"/>
       <c r="G789" s="98" t="s">
         <v>379</v>
       </c>
@@ -24769,7 +24784,7 @@
       <c r="E791" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F791" s="333" t="s">
+      <c r="F791" s="332" t="s">
         <v>297</v>
       </c>
       <c r="G791" s="94" t="s">
@@ -24795,7 +24810,7 @@
       <c r="E792" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F792" s="348"/>
+      <c r="F792" s="347"/>
       <c r="G792" s="136" t="s">
         <v>385</v>
       </c>
@@ -24819,7 +24834,7 @@
       <c r="E793" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F793" s="348"/>
+      <c r="F793" s="347"/>
       <c r="G793" s="136" t="s">
         <v>385</v>
       </c>
@@ -24843,7 +24858,7 @@
       <c r="E794" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F794" s="348"/>
+      <c r="F794" s="347"/>
       <c r="G794" s="136" t="s">
         <v>385</v>
       </c>
@@ -24867,7 +24882,7 @@
       <c r="E795" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F795" s="334"/>
+      <c r="F795" s="333"/>
       <c r="G795" s="98" t="s">
         <v>385</v>
       </c>
@@ -25019,7 +25034,7 @@
       <c r="E801" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F801" s="333" t="s">
+      <c r="F801" s="332" t="s">
         <v>388</v>
       </c>
       <c r="G801" s="94" t="s">
@@ -25045,7 +25060,7 @@
       <c r="E802" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F802" s="348"/>
+      <c r="F802" s="347"/>
       <c r="G802" s="136" t="s">
         <v>386</v>
       </c>
@@ -25069,7 +25084,7 @@
       <c r="E803" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F803" s="348"/>
+      <c r="F803" s="347"/>
       <c r="G803" s="136" t="s">
         <v>386</v>
       </c>
@@ -25093,7 +25108,7 @@
       <c r="E804" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F804" s="348"/>
+      <c r="F804" s="347"/>
       <c r="G804" s="136" t="s">
         <v>386</v>
       </c>
@@ -25117,7 +25132,7 @@
       <c r="E805" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F805" s="348"/>
+      <c r="F805" s="347"/>
       <c r="G805" s="136" t="s">
         <v>386</v>
       </c>
@@ -25141,7 +25156,7 @@
       <c r="E806" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F806" s="348"/>
+      <c r="F806" s="347"/>
       <c r="G806" s="144" t="s">
         <v>386</v>
       </c>
@@ -25639,7 +25654,7 @@
       <c r="E826" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F826" s="333" t="s">
+      <c r="F826" s="332" t="s">
         <v>395</v>
       </c>
       <c r="G826" s="94" t="s">
@@ -25665,7 +25680,7 @@
       <c r="E827" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F827" s="348"/>
+      <c r="F827" s="347"/>
       <c r="G827" s="136" t="s">
         <v>396</v>
       </c>
@@ -25689,7 +25704,7 @@
       <c r="E828" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F828" s="348"/>
+      <c r="F828" s="347"/>
       <c r="G828" s="136" t="s">
         <v>396</v>
       </c>
@@ -25713,7 +25728,7 @@
       <c r="E829" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F829" s="348"/>
+      <c r="F829" s="347"/>
       <c r="G829" s="136" t="s">
         <v>396</v>
       </c>
@@ -25737,7 +25752,7 @@
       <c r="E830" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F830" s="334"/>
+      <c r="F830" s="333"/>
       <c r="G830" s="98" t="s">
         <v>396</v>
       </c>
@@ -26035,7 +26050,7 @@
       <c r="E842" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F842" s="333" t="s">
+      <c r="F842" s="332" t="s">
         <v>402</v>
       </c>
       <c r="G842" s="94" t="s">
@@ -26063,7 +26078,7 @@
       <c r="E843" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F843" s="348"/>
+      <c r="F843" s="347"/>
       <c r="G843" s="136" t="s">
         <v>401</v>
       </c>
@@ -26087,7 +26102,7 @@
       <c r="E844" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F844" s="348"/>
+      <c r="F844" s="347"/>
       <c r="G844" s="136" t="s">
         <v>401</v>
       </c>
@@ -26111,7 +26126,7 @@
       <c r="E845" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F845" s="348"/>
+      <c r="F845" s="347"/>
       <c r="G845" s="136" t="s">
         <v>401</v>
       </c>
@@ -26135,7 +26150,7 @@
       <c r="E846" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F846" s="334"/>
+      <c r="F846" s="333"/>
       <c r="G846" s="98" t="s">
         <v>401</v>
       </c>
@@ -26361,7 +26376,7 @@
       <c r="E855" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F855" s="333" t="s">
+      <c r="F855" s="332" t="s">
         <v>402</v>
       </c>
       <c r="G855" s="94" t="s">
@@ -26387,7 +26402,7 @@
       <c r="E856" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F856" s="348"/>
+      <c r="F856" s="347"/>
       <c r="G856" s="136" t="s">
         <v>407</v>
       </c>
@@ -26411,7 +26426,7 @@
       <c r="E857" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F857" s="334"/>
+      <c r="F857" s="333"/>
       <c r="G857" s="98" t="s">
         <v>407</v>
       </c>
@@ -26515,7 +26530,7 @@
       <c r="E861" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F861" s="333" t="s">
+      <c r="F861" s="332" t="s">
         <v>409</v>
       </c>
       <c r="G861" s="94" t="s">
@@ -26541,7 +26556,7 @@
       <c r="E862" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F862" s="348"/>
+      <c r="F862" s="347"/>
       <c r="G862" s="136" t="s">
         <v>408</v>
       </c>
@@ -26565,7 +26580,7 @@
       <c r="E863" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F863" s="348"/>
+      <c r="F863" s="347"/>
       <c r="G863" s="136" t="s">
         <v>408</v>
       </c>
@@ -26589,7 +26604,7 @@
       <c r="E864" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F864" s="348"/>
+      <c r="F864" s="347"/>
       <c r="G864" s="136" t="s">
         <v>408</v>
       </c>
@@ -26613,7 +26628,7 @@
       <c r="E865" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F865" s="334"/>
+      <c r="F865" s="333"/>
       <c r="G865" s="98" t="s">
         <v>408</v>
       </c>
@@ -26637,7 +26652,7 @@
       <c r="E866" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F866" s="333" t="s">
+      <c r="F866" s="332" t="s">
         <v>405</v>
       </c>
       <c r="G866" s="136" t="s">
@@ -26663,7 +26678,7 @@
       <c r="E867" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F867" s="348"/>
+      <c r="F867" s="347"/>
       <c r="G867" s="136" t="s">
         <v>408</v>
       </c>
@@ -26687,7 +26702,7 @@
       <c r="E868" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F868" s="348"/>
+      <c r="F868" s="347"/>
       <c r="G868" s="136" t="s">
         <v>408</v>
       </c>
@@ -26711,7 +26726,7 @@
       <c r="E869" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F869" s="348"/>
+      <c r="F869" s="347"/>
       <c r="G869" s="136" t="s">
         <v>408</v>
       </c>
@@ -26735,7 +26750,7 @@
       <c r="E870" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F870" s="348"/>
+      <c r="F870" s="347"/>
       <c r="G870" s="136" t="s">
         <v>408</v>
       </c>
@@ -26759,7 +26774,7 @@
       <c r="E871" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F871" s="348"/>
+      <c r="F871" s="347"/>
       <c r="G871" s="136" t="s">
         <v>408</v>
       </c>
@@ -26783,7 +26798,7 @@
       <c r="E872" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F872" s="334"/>
+      <c r="F872" s="333"/>
       <c r="G872" s="98" t="s">
         <v>408</v>
       </c>
@@ -26937,7 +26952,7 @@
       <c r="E878" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F878" s="333" t="s">
+      <c r="F878" s="332" t="s">
         <v>414</v>
       </c>
       <c r="G878" s="94" t="s">
@@ -26963,7 +26978,7 @@
       <c r="E879" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F879" s="348"/>
+      <c r="F879" s="347"/>
       <c r="G879" s="136" t="s">
         <v>413</v>
       </c>
@@ -26987,7 +27002,7 @@
       <c r="E880" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F880" s="334"/>
+      <c r="F880" s="333"/>
       <c r="G880" s="98" t="s">
         <v>413</v>
       </c>
@@ -27011,7 +27026,7 @@
       <c r="E881" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F881" s="348" t="s">
+      <c r="F881" s="347" t="s">
         <v>415</v>
       </c>
       <c r="G881" s="136" t="s">
@@ -27037,7 +27052,7 @@
       <c r="E882" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F882" s="348"/>
+      <c r="F882" s="347"/>
       <c r="G882" s="136" t="s">
         <v>413</v>
       </c>
@@ -27061,7 +27076,7 @@
       <c r="E883" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F883" s="348"/>
+      <c r="F883" s="347"/>
       <c r="G883" s="136" t="s">
         <v>413</v>
       </c>
@@ -27085,7 +27100,7 @@
       <c r="E884" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F884" s="334"/>
+      <c r="F884" s="333"/>
       <c r="G884" s="98" t="s">
         <v>413</v>
       </c>
@@ -27239,7 +27254,7 @@
       <c r="E890" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F890" s="333" t="s">
+      <c r="F890" s="332" t="s">
         <v>420</v>
       </c>
       <c r="G890" s="94" t="s">
@@ -27265,7 +27280,7 @@
       <c r="E891" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F891" s="348"/>
+      <c r="F891" s="347"/>
       <c r="G891" s="136" t="s">
         <v>419</v>
       </c>
@@ -27289,7 +27304,7 @@
       <c r="E892" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F892" s="348"/>
+      <c r="F892" s="347"/>
       <c r="G892" s="136" t="s">
         <v>419</v>
       </c>
@@ -27313,7 +27328,7 @@
       <c r="E893" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F893" s="334"/>
+      <c r="F893" s="333"/>
       <c r="G893" s="98" t="s">
         <v>419</v>
       </c>
@@ -27337,7 +27352,7 @@
       <c r="E894" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F894" s="348" t="s">
+      <c r="F894" s="347" t="s">
         <v>415</v>
       </c>
       <c r="G894" s="136" t="s">
@@ -27363,7 +27378,7 @@
       <c r="E895" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F895" s="348"/>
+      <c r="F895" s="347"/>
       <c r="G895" s="136" t="s">
         <v>419</v>
       </c>
@@ -27387,7 +27402,7 @@
       <c r="E896" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F896" s="348"/>
+      <c r="F896" s="347"/>
       <c r="G896" s="136" t="s">
         <v>419</v>
       </c>
@@ -27411,7 +27426,7 @@
       <c r="E897" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F897" s="348"/>
+      <c r="F897" s="347"/>
       <c r="G897" s="136" t="s">
         <v>419</v>
       </c>
@@ -27435,7 +27450,7 @@
       <c r="E898" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F898" s="348"/>
+      <c r="F898" s="347"/>
       <c r="G898" s="136" t="s">
         <v>419</v>
       </c>
@@ -27459,7 +27474,7 @@
       <c r="E899" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F899" s="348"/>
+      <c r="F899" s="347"/>
       <c r="G899" s="136" t="s">
         <v>419</v>
       </c>
@@ -27483,7 +27498,7 @@
       <c r="E900" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F900" s="348"/>
+      <c r="F900" s="347"/>
       <c r="G900" s="144" t="s">
         <v>419</v>
       </c>
@@ -27911,7 +27926,7 @@
       <c r="E917" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F917" s="333" t="s">
+      <c r="F917" s="332" t="s">
         <v>429</v>
       </c>
       <c r="G917" s="94" t="s">
@@ -27937,7 +27952,7 @@
       <c r="E918" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F918" s="348"/>
+      <c r="F918" s="347"/>
       <c r="G918" s="136" t="s">
         <v>428</v>
       </c>
@@ -27963,7 +27978,7 @@
       <c r="E919" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F919" s="334"/>
+      <c r="F919" s="333"/>
       <c r="G919" s="98" t="s">
         <v>428</v>
       </c>
@@ -28065,7 +28080,7 @@
       <c r="E923" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F923" s="333" t="s">
+      <c r="F923" s="332" t="s">
         <v>430</v>
       </c>
       <c r="G923" s="94" t="s">
@@ -28091,7 +28106,7 @@
       <c r="E924" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F924" s="348"/>
+      <c r="F924" s="347"/>
       <c r="G924" s="136" t="s">
         <v>431</v>
       </c>
@@ -28165,7 +28180,7 @@
       <c r="E927" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F927" s="348"/>
+      <c r="F927" s="347"/>
       <c r="G927" s="136" t="s">
         <v>431</v>
       </c>
@@ -28189,7 +28204,7 @@
       <c r="E928" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F928" s="348"/>
+      <c r="F928" s="347"/>
       <c r="G928" s="136" t="s">
         <v>431</v>
       </c>
@@ -28213,7 +28228,7 @@
       <c r="E929" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F929" s="348"/>
+      <c r="F929" s="347"/>
       <c r="G929" s="136" t="s">
         <v>431</v>
       </c>
@@ -28237,7 +28252,7 @@
       <c r="E930" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F930" s="348"/>
+      <c r="F930" s="347"/>
       <c r="G930" s="144" t="s">
         <v>431</v>
       </c>
@@ -28417,7 +28432,7 @@
       <c r="E937" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F937" s="333" t="s">
+      <c r="F937" s="332" t="s">
         <v>435</v>
       </c>
       <c r="G937" s="94" t="s">
@@ -28443,7 +28458,7 @@
       <c r="E938" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F938" s="348"/>
+      <c r="F938" s="347"/>
       <c r="G938" s="136" t="s">
         <v>434</v>
       </c>
@@ -28467,7 +28482,7 @@
       <c r="E939" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F939" s="348"/>
+      <c r="F939" s="347"/>
       <c r="G939" s="136" t="s">
         <v>434</v>
       </c>
@@ -28493,7 +28508,7 @@
       <c r="E940" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F940" s="348"/>
+      <c r="F940" s="347"/>
       <c r="G940" s="136" t="s">
         <v>434</v>
       </c>
@@ -28517,7 +28532,7 @@
       <c r="E941" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F941" s="334"/>
+      <c r="F941" s="333"/>
       <c r="G941" s="98" t="s">
         <v>434</v>
       </c>
@@ -28693,7 +28708,7 @@
       <c r="E948" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F948" s="333" t="s">
+      <c r="F948" s="332" t="s">
         <v>395</v>
       </c>
       <c r="G948" s="94" t="s">
@@ -28719,7 +28734,7 @@
       <c r="E949" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F949" s="348"/>
+      <c r="F949" s="347"/>
       <c r="G949" s="136" t="s">
         <v>437</v>
       </c>
@@ -28743,7 +28758,7 @@
       <c r="E950" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F950" s="348"/>
+      <c r="F950" s="347"/>
       <c r="G950" s="136" t="s">
         <v>437</v>
       </c>
@@ -28767,7 +28782,7 @@
       <c r="E951" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F951" s="348"/>
+      <c r="F951" s="347"/>
       <c r="G951" s="136" t="s">
         <v>437</v>
       </c>
@@ -28791,7 +28806,7 @@
       <c r="E952" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F952" s="334"/>
+      <c r="F952" s="333"/>
       <c r="G952" s="98" t="s">
         <v>437</v>
       </c>
@@ -29117,7 +29132,7 @@
       <c r="E965" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F965" s="333" t="s">
+      <c r="F965" s="332" t="s">
         <v>323</v>
       </c>
       <c r="G965" s="94" t="s">
@@ -29143,7 +29158,7 @@
       <c r="E966" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F966" s="348"/>
+      <c r="F966" s="347"/>
       <c r="G966" s="136" t="s">
         <v>442</v>
       </c>
@@ -29169,7 +29184,7 @@
       <c r="E967" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F967" s="348"/>
+      <c r="F967" s="347"/>
       <c r="G967" s="136" t="s">
         <v>442</v>
       </c>
@@ -29193,7 +29208,7 @@
       <c r="E968" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F968" s="348"/>
+      <c r="F968" s="347"/>
       <c r="G968" s="136" t="s">
         <v>442</v>
       </c>
@@ -29217,7 +29232,7 @@
       <c r="E969" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F969" s="334"/>
+      <c r="F969" s="333"/>
       <c r="G969" s="98" t="s">
         <v>442</v>
       </c>
@@ -29517,7 +29532,7 @@
       <c r="E981" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F981" s="333" t="s">
+      <c r="F981" s="332" t="s">
         <v>448</v>
       </c>
       <c r="G981" s="94" t="s">
@@ -29543,7 +29558,7 @@
       <c r="E982" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F982" s="348"/>
+      <c r="F982" s="347"/>
       <c r="G982" s="136" t="s">
         <v>447</v>
       </c>
@@ -29569,7 +29584,7 @@
       <c r="E983" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F983" s="348"/>
+      <c r="F983" s="347"/>
       <c r="G983" s="136" t="s">
         <v>447</v>
       </c>
@@ -29593,7 +29608,7 @@
       <c r="E984" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F984" s="348"/>
+      <c r="F984" s="347"/>
       <c r="G984" s="136" t="s">
         <v>447</v>
       </c>
@@ -29617,7 +29632,7 @@
       <c r="E985" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F985" s="334"/>
+      <c r="F985" s="333"/>
       <c r="G985" s="98" t="s">
         <v>447</v>
       </c>
@@ -29771,7 +29786,7 @@
       <c r="E991" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F991" s="333" t="s">
+      <c r="F991" s="332" t="s">
         <v>451</v>
       </c>
       <c r="G991" s="94" t="s">
@@ -29797,7 +29812,7 @@
       <c r="E992" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F992" s="348"/>
+      <c r="F992" s="347"/>
       <c r="G992" s="136" t="s">
         <v>449</v>
       </c>
@@ -29821,7 +29836,7 @@
       <c r="E993" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F993" s="348"/>
+      <c r="F993" s="347"/>
       <c r="G993" s="136" t="s">
         <v>449</v>
       </c>
@@ -29845,7 +29860,7 @@
       <c r="E994" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F994" s="348"/>
+      <c r="F994" s="347"/>
       <c r="G994" s="136" t="s">
         <v>449</v>
       </c>
@@ -29869,7 +29884,7 @@
       <c r="E995" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F995" s="348"/>
+      <c r="F995" s="347"/>
       <c r="G995" s="136" t="s">
         <v>449</v>
       </c>
@@ -29893,7 +29908,7 @@
       <c r="E996" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F996" s="348"/>
+      <c r="F996" s="347"/>
       <c r="G996" s="136" t="s">
         <v>449</v>
       </c>
@@ -29917,7 +29932,7 @@
       <c r="E997" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F997" s="348"/>
+      <c r="F997" s="347"/>
       <c r="G997" s="136" t="s">
         <v>449</v>
       </c>
@@ -29941,7 +29956,7 @@
       <c r="E998" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F998" s="348"/>
+      <c r="F998" s="347"/>
       <c r="G998" s="144" t="s">
         <v>449</v>
       </c>
@@ -30095,7 +30110,7 @@
       <c r="E1004" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1004" s="333" t="s">
+      <c r="F1004" s="332" t="s">
         <v>455</v>
       </c>
       <c r="G1004" s="94" t="s">
@@ -30121,7 +30136,7 @@
       <c r="E1005" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1005" s="348"/>
+      <c r="F1005" s="347"/>
       <c r="G1005" s="136" t="s">
         <v>454</v>
       </c>
@@ -30145,7 +30160,7 @@
       <c r="E1006" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1006" s="348"/>
+      <c r="F1006" s="347"/>
       <c r="G1006" s="136" t="s">
         <v>454</v>
       </c>
@@ -30171,7 +30186,7 @@
       <c r="E1007" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1007" s="348"/>
+      <c r="F1007" s="347"/>
       <c r="G1007" s="136" t="s">
         <v>454</v>
       </c>
@@ -30195,7 +30210,7 @@
       <c r="E1008" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1008" s="334"/>
+      <c r="F1008" s="333"/>
       <c r="G1008" s="98" t="s">
         <v>454</v>
       </c>
@@ -30395,7 +30410,7 @@
       <c r="E1016" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1016" s="333" t="s">
+      <c r="F1016" s="332" t="s">
         <v>297</v>
       </c>
       <c r="G1016" s="94" t="s">
@@ -30421,7 +30436,7 @@
       <c r="E1017" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1017" s="348"/>
+      <c r="F1017" s="347"/>
       <c r="G1017" s="136" t="s">
         <v>457</v>
       </c>
@@ -30447,7 +30462,7 @@
       <c r="E1018" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1018" s="348"/>
+      <c r="F1018" s="347"/>
       <c r="G1018" s="136" t="s">
         <v>457</v>
       </c>
@@ -30471,7 +30486,7 @@
       <c r="E1019" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1019" s="348"/>
+      <c r="F1019" s="347"/>
       <c r="G1019" s="136" t="s">
         <v>457</v>
       </c>
@@ -30495,7 +30510,7 @@
       <c r="E1020" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1020" s="334"/>
+      <c r="F1020" s="333"/>
       <c r="G1020" s="98" t="s">
         <v>457</v>
       </c>
@@ -30649,7 +30664,7 @@
       <c r="E1026" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F1026" s="333" t="s">
+      <c r="F1026" s="332" t="s">
         <v>459</v>
       </c>
       <c r="G1026" s="94" t="s">
@@ -30675,7 +30690,7 @@
       <c r="E1027" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1027" s="348"/>
+      <c r="F1027" s="347"/>
       <c r="G1027" s="136" t="s">
         <v>458</v>
       </c>
@@ -30699,7 +30714,7 @@
       <c r="E1028" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1028" s="348"/>
+      <c r="F1028" s="347"/>
       <c r="G1028" s="136" t="s">
         <v>458</v>
       </c>
@@ -30723,7 +30738,7 @@
       <c r="E1029" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1029" s="348"/>
+      <c r="F1029" s="347"/>
       <c r="G1029" s="136" t="s">
         <v>458</v>
       </c>
@@ -30747,7 +30762,7 @@
       <c r="E1030" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1030" s="348"/>
+      <c r="F1030" s="347"/>
       <c r="G1030" s="136" t="s">
         <v>458</v>
       </c>
@@ -30771,7 +30786,7 @@
       <c r="E1031" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1031" s="348"/>
+      <c r="F1031" s="347"/>
       <c r="G1031" s="136" t="s">
         <v>458</v>
       </c>
@@ -30795,7 +30810,7 @@
       <c r="E1032" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F1032" s="348"/>
+      <c r="F1032" s="347"/>
       <c r="G1032" s="144" t="s">
         <v>458</v>
       </c>
@@ -30947,7 +30962,7 @@
       <c r="E1038" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1038" s="333" t="s">
+      <c r="F1038" s="332" t="s">
         <v>461</v>
       </c>
       <c r="G1038" s="94" t="s">
@@ -30973,7 +30988,7 @@
       <c r="E1039" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1039" s="348"/>
+      <c r="F1039" s="347"/>
       <c r="G1039" s="136" t="s">
         <v>465</v>
       </c>
@@ -30997,7 +31012,7 @@
       <c r="E1040" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1040" s="348"/>
+      <c r="F1040" s="347"/>
       <c r="G1040" s="136" t="s">
         <v>465</v>
       </c>
@@ -31023,7 +31038,7 @@
       <c r="E1041" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1041" s="348"/>
+      <c r="F1041" s="347"/>
       <c r="G1041" s="136" t="s">
         <v>465</v>
       </c>
@@ -31047,7 +31062,7 @@
       <c r="E1042" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1042" s="334"/>
+      <c r="F1042" s="333"/>
       <c r="G1042" s="98" t="s">
         <v>465</v>
       </c>
@@ -31499,7 +31514,7 @@
       <c r="E1060" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F1060" s="333" t="s">
+      <c r="F1060" s="332" t="s">
         <v>462</v>
       </c>
       <c r="G1060" s="94" t="s">
@@ -31525,7 +31540,7 @@
       <c r="E1061" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1061" s="348"/>
+      <c r="F1061" s="347"/>
       <c r="G1061" s="136" t="s">
         <v>466</v>
       </c>
@@ -31549,7 +31564,7 @@
       <c r="E1062" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1062" s="348"/>
+      <c r="F1062" s="347"/>
       <c r="G1062" s="136" t="s">
         <v>466</v>
       </c>
@@ -31573,7 +31588,7 @@
       <c r="E1063" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1063" s="348"/>
+      <c r="F1063" s="347"/>
       <c r="G1063" s="136" t="s">
         <v>466</v>
       </c>
@@ -31597,7 +31612,7 @@
       <c r="E1064" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1064" s="348"/>
+      <c r="F1064" s="347"/>
       <c r="G1064" s="136" t="s">
         <v>466</v>
       </c>
@@ -31621,7 +31636,7 @@
       <c r="E1065" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1065" s="348"/>
+      <c r="F1065" s="347"/>
       <c r="G1065" s="136" t="s">
         <v>466</v>
       </c>
@@ -31645,7 +31660,7 @@
       <c r="E1066" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F1066" s="348"/>
+      <c r="F1066" s="347"/>
       <c r="G1066" s="144" t="s">
         <v>466</v>
       </c>
@@ -31799,7 +31814,7 @@
       <c r="E1072" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1072" s="333" t="s">
+      <c r="F1072" s="332" t="s">
         <v>473</v>
       </c>
       <c r="G1072" s="94" t="s">
@@ -31825,7 +31840,7 @@
       <c r="E1073" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1073" s="348"/>
+      <c r="F1073" s="347"/>
       <c r="G1073" s="136" t="s">
         <v>472</v>
       </c>
@@ -31849,7 +31864,7 @@
       <c r="E1074" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1074" s="348"/>
+      <c r="F1074" s="347"/>
       <c r="G1074" s="136" t="s">
         <v>472</v>
       </c>
@@ -31875,7 +31890,7 @@
       <c r="E1075" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1075" s="348"/>
+      <c r="F1075" s="347"/>
       <c r="G1075" s="136" t="s">
         <v>472</v>
       </c>
@@ -31899,7 +31914,7 @@
       <c r="E1076" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1076" s="334"/>
+      <c r="F1076" s="333"/>
       <c r="G1076" s="98" t="s">
         <v>472</v>
       </c>
@@ -32075,7 +32090,7 @@
       <c r="E1083" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1083" s="333" t="s">
+      <c r="F1083" s="332" t="s">
         <v>412</v>
       </c>
       <c r="G1083" s="94" t="s">
@@ -32101,7 +32116,7 @@
       <c r="E1084" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1084" s="348"/>
+      <c r="F1084" s="347"/>
       <c r="G1084" s="136" t="s">
         <v>478</v>
       </c>
@@ -32127,7 +32142,7 @@
       <c r="E1085" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1085" s="348"/>
+      <c r="F1085" s="347"/>
       <c r="G1085" s="136" t="s">
         <v>478</v>
       </c>
@@ -32151,7 +32166,7 @@
       <c r="E1086" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1086" s="348"/>
+      <c r="F1086" s="347"/>
       <c r="G1086" s="136" t="s">
         <v>478</v>
       </c>
@@ -32175,7 +32190,7 @@
       <c r="E1087" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1087" s="334"/>
+      <c r="F1087" s="333"/>
       <c r="G1087" s="98" t="s">
         <v>478</v>
       </c>
@@ -32329,7 +32344,7 @@
       <c r="E1093" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F1093" s="333" t="s">
+      <c r="F1093" s="332" t="s">
         <v>462</v>
       </c>
       <c r="G1093" s="94" t="s">
@@ -32355,7 +32370,7 @@
       <c r="E1094" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="F1094" s="348"/>
+      <c r="F1094" s="347"/>
       <c r="G1094" s="146" t="s">
         <v>476</v>
       </c>
@@ -32379,7 +32394,7 @@
       <c r="E1095" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="F1095" s="348"/>
+      <c r="F1095" s="347"/>
       <c r="G1095" s="146" t="s">
         <v>476</v>
       </c>
@@ -32403,7 +32418,7 @@
       <c r="E1096" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="F1096" s="348"/>
+      <c r="F1096" s="347"/>
       <c r="G1096" s="146" t="s">
         <v>476</v>
       </c>
@@ -32427,7 +32442,7 @@
       <c r="E1097" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="F1097" s="348"/>
+      <c r="F1097" s="347"/>
       <c r="G1097" s="146" t="s">
         <v>476</v>
       </c>
@@ -32451,7 +32466,7 @@
       <c r="E1098" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="F1098" s="348"/>
+      <c r="F1098" s="347"/>
       <c r="G1098" s="146" t="s">
         <v>476</v>
       </c>
@@ -32475,7 +32490,7 @@
       <c r="E1099" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F1099" s="348"/>
+      <c r="F1099" s="347"/>
       <c r="G1099" s="144" t="s">
         <v>476</v>
       </c>
@@ -32655,7 +32670,7 @@
       <c r="E1106" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1106" s="333" t="s">
+      <c r="F1106" s="332" t="s">
         <v>361</v>
       </c>
       <c r="G1106" s="94" t="s">
@@ -32681,7 +32696,7 @@
       <c r="E1107" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1107" s="348"/>
+      <c r="F1107" s="347"/>
       <c r="G1107" s="136" t="s">
         <v>481</v>
       </c>
@@ -32705,7 +32720,7 @@
       <c r="E1108" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1108" s="348"/>
+      <c r="F1108" s="347"/>
       <c r="G1108" s="136" t="s">
         <v>481</v>
       </c>
@@ -32731,7 +32746,7 @@
       <c r="E1109" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1109" s="348"/>
+      <c r="F1109" s="347"/>
       <c r="G1109" s="136" t="s">
         <v>481</v>
       </c>
@@ -32755,7 +32770,7 @@
       <c r="E1110" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1110" s="334"/>
+      <c r="F1110" s="333"/>
       <c r="G1110" s="98" t="s">
         <v>481</v>
       </c>
@@ -32931,7 +32946,7 @@
       <c r="E1117" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1117" s="333" t="s">
+      <c r="F1117" s="332" t="s">
         <v>487</v>
       </c>
       <c r="G1117" s="94" t="s">
@@ -32959,7 +32974,7 @@
       <c r="E1118" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1118" s="348"/>
+      <c r="F1118" s="347"/>
       <c r="G1118" s="136" t="s">
         <v>484</v>
       </c>
@@ -32983,7 +32998,7 @@
       <c r="E1119" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1119" s="348"/>
+      <c r="F1119" s="347"/>
       <c r="G1119" s="136" t="s">
         <v>484</v>
       </c>
@@ -33007,7 +33022,7 @@
       <c r="E1120" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1120" s="348"/>
+      <c r="F1120" s="347"/>
       <c r="G1120" s="136" t="s">
         <v>484</v>
       </c>
@@ -33033,7 +33048,7 @@
       <c r="E1121" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1121" s="334"/>
+      <c r="F1121" s="333"/>
       <c r="G1121" s="98" t="s">
         <v>484</v>
       </c>
@@ -33187,7 +33202,7 @@
       <c r="E1127" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F1127" s="333" t="s">
+      <c r="F1127" s="332" t="s">
         <v>451</v>
       </c>
       <c r="G1127" s="94" t="s">
@@ -33213,7 +33228,7 @@
       <c r="E1128" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1128" s="348"/>
+      <c r="F1128" s="347"/>
       <c r="G1128" s="136" t="s">
         <v>485</v>
       </c>
@@ -33237,7 +33252,7 @@
       <c r="E1129" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1129" s="348"/>
+      <c r="F1129" s="347"/>
       <c r="G1129" s="136" t="s">
         <v>485</v>
       </c>
@@ -33261,7 +33276,7 @@
       <c r="E1130" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1130" s="348"/>
+      <c r="F1130" s="347"/>
       <c r="G1130" s="136" t="s">
         <v>485</v>
       </c>
@@ -33285,7 +33300,7 @@
       <c r="E1131" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1131" s="348"/>
+      <c r="F1131" s="347"/>
       <c r="G1131" s="136" t="s">
         <v>485</v>
       </c>
@@ -33309,7 +33324,7 @@
       <c r="E1132" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1132" s="348"/>
+      <c r="F1132" s="347"/>
       <c r="G1132" s="136" t="s">
         <v>485</v>
       </c>
@@ -33333,7 +33348,7 @@
       <c r="E1133" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F1133" s="348"/>
+      <c r="F1133" s="347"/>
       <c r="G1133" s="144" t="s">
         <v>485</v>
       </c>
@@ -33511,7 +33526,7 @@
       <c r="E1140" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1140" s="333" t="s">
+      <c r="F1140" s="332" t="s">
         <v>491</v>
       </c>
       <c r="G1140" s="94" t="s">
@@ -33537,7 +33552,7 @@
       <c r="E1141" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1141" s="348"/>
+      <c r="F1141" s="347"/>
       <c r="G1141" s="136" t="s">
         <v>490</v>
       </c>
@@ -33561,7 +33576,7 @@
       <c r="E1142" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1142" s="348"/>
+      <c r="F1142" s="347"/>
       <c r="G1142" s="136" t="s">
         <v>490</v>
       </c>
@@ -33587,7 +33602,7 @@
       <c r="E1143" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1143" s="348"/>
+      <c r="F1143" s="347"/>
       <c r="G1143" s="136" t="s">
         <v>490</v>
       </c>
@@ -33611,7 +33626,7 @@
       <c r="E1144" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1144" s="334"/>
+      <c r="F1144" s="333"/>
       <c r="G1144" s="98" t="s">
         <v>490</v>
       </c>
@@ -33835,7 +33850,7 @@
       <c r="E1153" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1153" s="333" t="s">
+      <c r="F1153" s="332" t="s">
         <v>493</v>
       </c>
       <c r="G1153" s="94" t="s">
@@ -33861,7 +33876,7 @@
       <c r="E1154" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1154" s="348"/>
+      <c r="F1154" s="347"/>
       <c r="G1154" s="136" t="s">
         <v>495</v>
       </c>
@@ -33887,7 +33902,7 @@
       <c r="E1155" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1155" s="348"/>
+      <c r="F1155" s="347"/>
       <c r="G1155" s="136" t="s">
         <v>495</v>
       </c>
@@ -33911,7 +33926,7 @@
       <c r="E1156" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1156" s="348"/>
+      <c r="F1156" s="347"/>
       <c r="G1156" s="136" t="s">
         <v>495</v>
       </c>
@@ -33935,7 +33950,7 @@
       <c r="E1157" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1157" s="348"/>
+      <c r="F1157" s="347"/>
       <c r="G1157" s="136" t="s">
         <v>495</v>
       </c>
@@ -33961,7 +33976,7 @@
       <c r="E1158" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1158" s="334"/>
+      <c r="F1158" s="333"/>
       <c r="G1158" s="98" t="s">
         <v>495</v>
       </c>
@@ -34115,7 +34130,7 @@
       <c r="E1164" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F1164" s="333" t="s">
+      <c r="F1164" s="332" t="s">
         <v>451</v>
       </c>
       <c r="G1164" s="94" t="s">
@@ -34141,7 +34156,7 @@
       <c r="E1165" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="F1165" s="348"/>
+      <c r="F1165" s="347"/>
       <c r="G1165" s="136" t="s">
         <v>496</v>
       </c>
@@ -34165,7 +34180,7 @@
       <c r="E1166" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="F1166" s="348"/>
+      <c r="F1166" s="347"/>
       <c r="G1166" s="136" t="s">
         <v>496</v>
       </c>
@@ -34189,7 +34204,7 @@
       <c r="E1167" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="F1167" s="348"/>
+      <c r="F1167" s="347"/>
       <c r="G1167" s="136" t="s">
         <v>496</v>
       </c>
@@ -34213,7 +34228,7 @@
       <c r="E1168" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="F1168" s="348"/>
+      <c r="F1168" s="347"/>
       <c r="G1168" s="136" t="s">
         <v>496</v>
       </c>
@@ -34237,7 +34252,7 @@
       <c r="E1169" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="F1169" s="348"/>
+      <c r="F1169" s="347"/>
       <c r="G1169" s="136" t="s">
         <v>496</v>
       </c>
@@ -34261,7 +34276,7 @@
       <c r="E1170" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="F1170" s="348"/>
+      <c r="F1170" s="347"/>
       <c r="G1170" s="136" t="s">
         <v>496</v>
       </c>
@@ -34285,7 +34300,7 @@
       <c r="E1171" s="249" t="s">
         <v>45</v>
       </c>
-      <c r="F1171" s="348"/>
+      <c r="F1171" s="347"/>
       <c r="G1171" s="144" t="s">
         <v>496</v>
       </c>
@@ -34437,7 +34452,7 @@
       <c r="E1177" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1177" s="333" t="s">
+      <c r="F1177" s="332" t="s">
         <v>501</v>
       </c>
       <c r="G1177" s="94" t="s">
@@ -34463,7 +34478,7 @@
       <c r="E1178" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1178" s="348"/>
+      <c r="F1178" s="347"/>
       <c r="G1178" s="136" t="s">
         <v>499</v>
       </c>
@@ -34487,7 +34502,7 @@
       <c r="E1179" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1179" s="348"/>
+      <c r="F1179" s="347"/>
       <c r="G1179" s="136" t="s">
         <v>499</v>
       </c>
@@ -34511,7 +34526,7 @@
       <c r="E1180" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1180" s="348"/>
+      <c r="F1180" s="347"/>
       <c r="G1180" s="136" t="s">
         <v>499</v>
       </c>
@@ -34535,7 +34550,7 @@
       <c r="E1181" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1181" s="334"/>
+      <c r="F1181" s="333"/>
       <c r="G1181" s="98" t="s">
         <v>499</v>
       </c>
@@ -34735,7 +34750,7 @@
       <c r="E1189" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1189" s="333" t="s">
+      <c r="F1189" s="332" t="s">
         <v>506</v>
       </c>
       <c r="G1189" s="94" t="s">
@@ -34761,7 +34776,7 @@
       <c r="E1190" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1190" s="348"/>
+      <c r="F1190" s="347"/>
       <c r="G1190" s="136" t="s">
         <v>504</v>
       </c>
@@ -34787,7 +34802,7 @@
       <c r="E1191" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1191" s="348"/>
+      <c r="F1191" s="347"/>
       <c r="G1191" s="136" t="s">
         <v>504</v>
       </c>
@@ -34811,7 +34826,7 @@
       <c r="E1192" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1192" s="348"/>
+      <c r="F1192" s="347"/>
       <c r="G1192" s="136" t="s">
         <v>504</v>
       </c>
@@ -34835,7 +34850,7 @@
       <c r="E1193" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="F1193" s="348"/>
+      <c r="F1193" s="347"/>
       <c r="G1193" s="136" t="s">
         <v>504</v>
       </c>
@@ -34861,7 +34876,7 @@
       <c r="E1194" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="F1194" s="334"/>
+      <c r="F1194" s="333"/>
       <c r="G1194" s="98" t="s">
         <v>504</v>
       </c>
@@ -35015,7 +35030,7 @@
       <c r="E1200" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="F1200" s="333" t="s">
+      <c r="F1200" s="332" t="s">
         <v>509</v>
       </c>
       <c r="G1200" s="94" t="s">
@@ -35041,7 +35056,7 @@
       <c r="E1201" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1201" s="348"/>
+      <c r="F1201" s="347"/>
       <c r="G1201" s="136" t="s">
         <v>505</v>
       </c>
@@ -35065,7 +35080,7 @@
       <c r="E1202" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="F1202" s="348"/>
+      <c r="F1202" s="347"/>
       <c r="G1202" s="136" t="s">
         <v>505</v>
       </c>
@@ -35089,7 +35104,7 @@
       <c r="E1203" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1203" s="348"/>
+      <c r="F1203" s="347"/>
       <c r="G1203" s="136" t="s">
         <v>505</v>
       </c>
@@ -35113,7 +35128,7 @@
       <c r="E1204" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1204" s="348"/>
+      <c r="F1204" s="347"/>
       <c r="G1204" s="136" t="s">
         <v>505</v>
       </c>
@@ -35137,7 +35152,7 @@
       <c r="E1205" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1205" s="348"/>
+      <c r="F1205" s="347"/>
       <c r="G1205" s="136" t="s">
         <v>505</v>
       </c>
@@ -35161,7 +35176,7 @@
       <c r="E1206" s="136" t="s">
         <v>508</v>
       </c>
-      <c r="F1206" s="348"/>
+      <c r="F1206" s="347"/>
       <c r="G1206" s="136" t="s">
         <v>505</v>
       </c>
@@ -35185,7 +35200,7 @@
       <c r="E1207" s="136" t="s">
         <v>508</v>
       </c>
-      <c r="F1207" s="348"/>
+      <c r="F1207" s="347"/>
       <c r="G1207" s="136" t="s">
         <v>505</v>
       </c>
@@ -35209,7 +35224,7 @@
       <c r="E1208" s="136" t="s">
         <v>508</v>
       </c>
-      <c r="F1208" s="348"/>
+      <c r="F1208" s="347"/>
       <c r="G1208" s="136" t="s">
         <v>505</v>
       </c>
@@ -35233,7 +35248,7 @@
       <c r="E1209" s="98" t="s">
         <v>508</v>
       </c>
-      <c r="F1209" s="334"/>
+      <c r="F1209" s="333"/>
       <c r="G1209" s="98" t="s">
         <v>505</v>
       </c>
@@ -35821,7 +35836,7 @@
       </c>
     </row>
     <row r="1233" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1233" s="439">
+      <c r="A1233" s="438">
         <f>MAX(A1212:A1232)+1</f>
         <v>235</v>
       </c>
@@ -35848,7 +35863,7 @@
       </c>
     </row>
     <row r="1234" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1234" s="440"/>
+      <c r="A1234" s="439"/>
       <c r="B1234" s="223" t="s">
         <v>516</v>
       </c>
@@ -35872,7 +35887,7 @@
       </c>
     </row>
     <row r="1235" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1235" s="440"/>
+      <c r="A1235" s="439"/>
       <c r="B1235" s="223" t="s">
         <v>516</v>
       </c>
@@ -35898,7 +35913,7 @@
       </c>
     </row>
     <row r="1236" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1236" s="440"/>
+      <c r="A1236" s="439"/>
       <c r="B1236" s="223" t="s">
         <v>516</v>
       </c>
@@ -35922,7 +35937,7 @@
       </c>
     </row>
     <row r="1237" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1237" s="441"/>
+      <c r="A1237" s="440"/>
       <c r="B1237" s="128" t="s">
         <v>522</v>
       </c>
@@ -35963,7 +35978,7 @@
       <c r="E1238" s="94" t="s">
         <v>519</v>
       </c>
-      <c r="F1238" s="333" t="s">
+      <c r="F1238" s="332" t="s">
         <v>521</v>
       </c>
       <c r="G1238" s="94" t="s">
@@ -35990,7 +36005,7 @@
       <c r="E1239" s="136" t="s">
         <v>519</v>
       </c>
-      <c r="F1239" s="348"/>
+      <c r="F1239" s="347"/>
       <c r="G1239" s="136" t="s">
         <v>518</v>
       </c>
@@ -36014,7 +36029,7 @@
       <c r="E1240" s="136" t="s">
         <v>519</v>
       </c>
-      <c r="F1240" s="348"/>
+      <c r="F1240" s="347"/>
       <c r="G1240" s="136" t="s">
         <v>518</v>
       </c>
@@ -36039,7 +36054,7 @@
       <c r="E1241" s="136" t="s">
         <v>519</v>
       </c>
-      <c r="F1241" s="348"/>
+      <c r="F1241" s="347"/>
       <c r="G1241" s="136" t="s">
         <v>518</v>
       </c>
@@ -36063,7 +36078,7 @@
       <c r="E1242" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1242" s="348"/>
+      <c r="F1242" s="347"/>
       <c r="G1242" s="136" t="s">
         <v>518</v>
       </c>
@@ -36087,7 +36102,7 @@
       <c r="E1243" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F1243" s="334"/>
+      <c r="F1243" s="333"/>
       <c r="G1243" s="98" t="s">
         <v>518</v>
       </c>
@@ -36889,7 +36904,7 @@
       <c r="E1275" s="94" t="s">
         <v>519</v>
       </c>
-      <c r="F1275" s="333" t="s">
+      <c r="F1275" s="332" t="s">
         <v>533</v>
       </c>
       <c r="G1275" s="94" t="s">
@@ -36915,7 +36930,7 @@
       <c r="E1276" s="136" t="s">
         <v>519</v>
       </c>
-      <c r="F1276" s="348"/>
+      <c r="F1276" s="347"/>
       <c r="G1276" s="136" t="s">
         <v>532</v>
       </c>
@@ -36939,7 +36954,7 @@
       <c r="E1277" s="136" t="s">
         <v>519</v>
       </c>
-      <c r="F1277" s="348"/>
+      <c r="F1277" s="347"/>
       <c r="G1277" s="136" t="s">
         <v>532</v>
       </c>
@@ -36963,7 +36978,7 @@
       <c r="E1278" s="136" t="s">
         <v>519</v>
       </c>
-      <c r="F1278" s="348"/>
+      <c r="F1278" s="347"/>
       <c r="G1278" s="136" t="s">
         <v>532</v>
       </c>
@@ -36987,7 +37002,7 @@
       <c r="E1279" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1279" s="348"/>
+      <c r="F1279" s="347"/>
       <c r="G1279" s="136" t="s">
         <v>532</v>
       </c>
@@ -37011,7 +37026,7 @@
       <c r="E1280" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1280" s="348"/>
+      <c r="F1280" s="347"/>
       <c r="G1280" s="136" t="s">
         <v>532</v>
       </c>
@@ -37035,7 +37050,7 @@
       <c r="E1281" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F1281" s="348"/>
+      <c r="F1281" s="347"/>
       <c r="G1281" s="144" t="s">
         <v>532</v>
       </c>
@@ -37766,7 +37781,7 @@
       <c r="E1310" s="94" t="s">
         <v>519</v>
       </c>
-      <c r="F1310" s="333" t="s">
+      <c r="F1310" s="332" t="s">
         <v>541</v>
       </c>
       <c r="G1310" s="94" t="s">
@@ -37792,7 +37807,7 @@
       <c r="E1311" s="136" t="s">
         <v>519</v>
       </c>
-      <c r="F1311" s="348"/>
+      <c r="F1311" s="347"/>
       <c r="G1311" s="136" t="s">
         <v>540</v>
       </c>
@@ -37816,7 +37831,7 @@
       <c r="E1312" s="136" t="s">
         <v>519</v>
       </c>
-      <c r="F1312" s="348"/>
+      <c r="F1312" s="347"/>
       <c r="G1312" s="136" t="s">
         <v>540</v>
       </c>
@@ -37840,7 +37855,7 @@
       <c r="E1313" s="136" t="s">
         <v>519</v>
       </c>
-      <c r="F1313" s="348"/>
+      <c r="F1313" s="347"/>
       <c r="G1313" s="136" t="s">
         <v>540</v>
       </c>
@@ -37864,7 +37879,7 @@
       <c r="E1314" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1314" s="348"/>
+      <c r="F1314" s="347"/>
       <c r="G1314" s="136" t="s">
         <v>540</v>
       </c>
@@ -37888,7 +37903,7 @@
       <c r="E1315" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1315" s="348"/>
+      <c r="F1315" s="347"/>
       <c r="G1315" s="136" t="s">
         <v>540</v>
       </c>
@@ -37912,7 +37927,7 @@
       <c r="E1316" s="136" t="s">
         <v>45</v>
       </c>
-      <c r="F1316" s="348"/>
+      <c r="F1316" s="347"/>
       <c r="G1316" s="136" t="s">
         <v>540</v>
       </c>
@@ -37936,7 +37951,7 @@
       <c r="E1317" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F1317" s="348"/>
+      <c r="F1317" s="347"/>
       <c r="G1317" s="144" t="s">
         <v>540</v>
       </c>
@@ -38263,7 +38278,7 @@
       <c r="E1330" s="256" t="s">
         <v>34</v>
       </c>
-      <c r="F1330" s="345" t="s">
+      <c r="F1330" s="344" t="s">
         <v>546</v>
       </c>
       <c r="G1330" s="256" t="s">
@@ -38289,7 +38304,7 @@
       <c r="E1331" s="252" t="s">
         <v>34</v>
       </c>
-      <c r="F1331" s="346"/>
+      <c r="F1331" s="345"/>
       <c r="G1331" s="252" t="s">
         <v>544</v>
       </c>
@@ -38313,7 +38328,7 @@
       <c r="E1332" s="252" t="s">
         <v>34</v>
       </c>
-      <c r="F1332" s="346"/>
+      <c r="F1332" s="345"/>
       <c r="G1332" s="252" t="s">
         <v>544</v>
       </c>
@@ -38337,7 +38352,7 @@
       <c r="E1333" s="260" t="s">
         <v>34</v>
       </c>
-      <c r="F1333" s="346"/>
+      <c r="F1333" s="345"/>
       <c r="G1333" s="260" t="s">
         <v>544</v>
       </c>
@@ -38364,7 +38379,7 @@
       <c r="E1334" s="94" t="s">
         <v>519</v>
       </c>
-      <c r="F1334" s="333" t="s">
+      <c r="F1334" s="332" t="s">
         <v>549</v>
       </c>
       <c r="G1334" s="94" t="s">
@@ -38390,7 +38405,7 @@
       <c r="E1335" s="146" t="s">
         <v>519</v>
       </c>
-      <c r="F1335" s="348"/>
+      <c r="F1335" s="347"/>
       <c r="G1335" s="146" t="s">
         <v>548</v>
       </c>
@@ -38414,7 +38429,7 @@
       <c r="E1336" s="146" t="s">
         <v>519</v>
       </c>
-      <c r="F1336" s="348"/>
+      <c r="F1336" s="347"/>
       <c r="G1336" s="146" t="s">
         <v>548</v>
       </c>
@@ -38438,7 +38453,7 @@
       <c r="E1337" s="146" t="s">
         <v>519</v>
       </c>
-      <c r="F1337" s="348"/>
+      <c r="F1337" s="347"/>
       <c r="G1337" s="146" t="s">
         <v>548</v>
       </c>
@@ -38462,7 +38477,7 @@
       <c r="E1338" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="F1338" s="348"/>
+      <c r="F1338" s="347"/>
       <c r="G1338" s="146" t="s">
         <v>548</v>
       </c>
@@ -38486,7 +38501,7 @@
       <c r="E1339" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="F1339" s="348"/>
+      <c r="F1339" s="347"/>
       <c r="G1339" s="146" t="s">
         <v>548</v>
       </c>
@@ -38510,7 +38525,7 @@
       <c r="E1340" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="F1340" s="348"/>
+      <c r="F1340" s="347"/>
       <c r="G1340" s="146" t="s">
         <v>548</v>
       </c>
@@ -38534,7 +38549,7 @@
       <c r="E1341" s="249" t="s">
         <v>45</v>
       </c>
-      <c r="F1341" s="348"/>
+      <c r="F1341" s="347"/>
       <c r="G1341" s="249" t="s">
         <v>548</v>
       </c>
@@ -38863,7 +38878,7 @@
       <c r="E1354" s="256" t="s">
         <v>519</v>
       </c>
-      <c r="F1354" s="345" t="s">
+      <c r="F1354" s="344" t="s">
         <v>549</v>
       </c>
       <c r="G1354" s="256" t="s">
@@ -38889,7 +38904,7 @@
       <c r="E1355" s="252" t="s">
         <v>519</v>
       </c>
-      <c r="F1355" s="346"/>
+      <c r="F1355" s="345"/>
       <c r="G1355" s="252" t="s">
         <v>554</v>
       </c>
@@ -38913,7 +38928,7 @@
       <c r="E1356" s="252" t="s">
         <v>519</v>
       </c>
-      <c r="F1356" s="346"/>
+      <c r="F1356" s="345"/>
       <c r="G1356" s="252" t="s">
         <v>554</v>
       </c>
@@ -38937,7 +38952,7 @@
       <c r="E1357" s="252" t="s">
         <v>519</v>
       </c>
-      <c r="F1357" s="346"/>
+      <c r="F1357" s="345"/>
       <c r="G1357" s="252" t="s">
         <v>554</v>
       </c>
@@ -38961,7 +38976,7 @@
       <c r="E1358" s="252" t="s">
         <v>45</v>
       </c>
-      <c r="F1358" s="346"/>
+      <c r="F1358" s="345"/>
       <c r="G1358" s="252" t="s">
         <v>554</v>
       </c>
@@ -38985,7 +39000,7 @@
       <c r="E1359" s="252" t="s">
         <v>45</v>
       </c>
-      <c r="F1359" s="346"/>
+      <c r="F1359" s="345"/>
       <c r="G1359" s="252" t="s">
         <v>554</v>
       </c>
@@ -39009,7 +39024,7 @@
       <c r="E1360" s="252" t="s">
         <v>45</v>
       </c>
-      <c r="F1360" s="346"/>
+      <c r="F1360" s="345"/>
       <c r="G1360" s="252" t="s">
         <v>554</v>
       </c>
@@ -39033,7 +39048,7 @@
       <c r="E1361" s="260" t="s">
         <v>45</v>
       </c>
-      <c r="F1361" s="346"/>
+      <c r="F1361" s="345"/>
       <c r="G1361" s="260" t="s">
         <v>554</v>
       </c>
@@ -39057,7 +39072,7 @@
       <c r="E1362" s="260" t="s">
         <v>34</v>
       </c>
-      <c r="F1362" s="346"/>
+      <c r="F1362" s="345"/>
       <c r="G1362" s="260" t="s">
         <v>554</v>
       </c>
@@ -39083,7 +39098,7 @@
       <c r="E1363" s="260" t="s">
         <v>45</v>
       </c>
-      <c r="F1363" s="346"/>
+      <c r="F1363" s="345"/>
       <c r="G1363" s="260" t="s">
         <v>554</v>
       </c>
@@ -39666,7 +39681,7 @@
       <c r="E1386" s="149" t="s">
         <v>519</v>
       </c>
-      <c r="F1386" s="339" t="s">
+      <c r="F1386" s="338" t="s">
         <v>533</v>
       </c>
       <c r="G1386" s="149" t="s">
@@ -39679,7 +39694,7 @@
       </c>
     </row>
     <row r="1387" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1387" s="348"/>
+      <c r="A1387" s="347"/>
       <c r="B1387" s="149" t="s">
         <v>560</v>
       </c>
@@ -39692,7 +39707,7 @@
       <c r="E1387" s="149" t="s">
         <v>519</v>
       </c>
-      <c r="F1387" s="339"/>
+      <c r="F1387" s="338"/>
       <c r="G1387" s="149" t="s">
         <v>559</v>
       </c>
@@ -39703,7 +39718,7 @@
       </c>
     </row>
     <row r="1388" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1388" s="348"/>
+      <c r="A1388" s="347"/>
       <c r="B1388" s="149" t="s">
         <v>560</v>
       </c>
@@ -39716,7 +39731,7 @@
       <c r="E1388" s="149" t="s">
         <v>519</v>
       </c>
-      <c r="F1388" s="339"/>
+      <c r="F1388" s="338"/>
       <c r="G1388" s="149" t="s">
         <v>559</v>
       </c>
@@ -39727,7 +39742,7 @@
       </c>
     </row>
     <row r="1389" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1389" s="348"/>
+      <c r="A1389" s="347"/>
       <c r="B1389" s="149" t="s">
         <v>560</v>
       </c>
@@ -39740,7 +39755,7 @@
       <c r="E1389" s="149" t="s">
         <v>519</v>
       </c>
-      <c r="F1389" s="339"/>
+      <c r="F1389" s="338"/>
       <c r="G1389" s="149" t="s">
         <v>559</v>
       </c>
@@ -39751,7 +39766,7 @@
       </c>
     </row>
     <row r="1390" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1390" s="348"/>
+      <c r="A1390" s="347"/>
       <c r="B1390" s="287" t="s">
         <v>560</v>
       </c>
@@ -39764,7 +39779,7 @@
       <c r="E1390" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="F1390" s="339"/>
+      <c r="F1390" s="338"/>
       <c r="G1390" s="149" t="s">
         <v>559</v>
       </c>
@@ -40119,7 +40134,7 @@
       <c r="E1404" s="290" t="s">
         <v>519</v>
       </c>
-      <c r="F1404" s="438"/>
+      <c r="F1404" s="437"/>
       <c r="G1404" s="290" t="s">
         <v>562</v>
       </c>
@@ -40143,7 +40158,7 @@
       <c r="E1405" s="290" t="s">
         <v>519</v>
       </c>
-      <c r="F1405" s="438"/>
+      <c r="F1405" s="437"/>
       <c r="G1405" s="290" t="s">
         <v>562</v>
       </c>
@@ -40167,7 +40182,7 @@
       <c r="E1406" s="290" t="s">
         <v>519</v>
       </c>
-      <c r="F1406" s="438"/>
+      <c r="F1406" s="437"/>
       <c r="G1406" s="290" t="s">
         <v>562</v>
       </c>
@@ -40191,7 +40206,7 @@
       <c r="E1407" s="290" t="s">
         <v>45</v>
       </c>
-      <c r="F1407" s="438"/>
+      <c r="F1407" s="437"/>
       <c r="G1407" s="290" t="s">
         <v>562</v>
       </c>
@@ -40215,7 +40230,7 @@
       <c r="E1408" s="290" t="s">
         <v>45</v>
       </c>
-      <c r="F1408" s="438"/>
+      <c r="F1408" s="437"/>
       <c r="G1408" s="290" t="s">
         <v>562</v>
       </c>
@@ -46297,7 +46312,7 @@
       <c r="H1648" s="290"/>
       <c r="I1648" s="290"/>
     </row>
-    <row r="1649" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1649" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1649" s="356"/>
       <c r="B1649" s="289" t="s">
         <v>629</v>
@@ -46320,7 +46335,7 @@
       </c>
       <c r="I1649" s="290"/>
     </row>
-    <row r="1650" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1650" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1650" s="356"/>
       <c r="B1650" s="289" t="s">
         <v>629</v>
@@ -46341,7 +46356,7 @@
       <c r="H1650" s="290"/>
       <c r="I1650" s="290"/>
     </row>
-    <row r="1651" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1651" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1651" s="356"/>
       <c r="B1651" s="289" t="s">
         <v>629</v>
@@ -46362,7 +46377,7 @@
       <c r="H1651" s="290"/>
       <c r="I1651" s="290"/>
     </row>
-    <row r="1652" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1652" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1652" s="356"/>
       <c r="B1652" s="289" t="s">
         <v>629</v>
@@ -46383,31 +46398,31 @@
       <c r="H1652" s="290"/>
       <c r="I1652" s="290"/>
     </row>
-    <row r="1653" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1653" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1653" s="356"/>
       <c r="B1653" s="307" t="s">
         <v>629</v>
       </c>
-      <c r="C1653" s="309" t="s">
+      <c r="C1653" s="308" t="s">
         <v>621</v>
       </c>
-      <c r="D1653" s="310">
+      <c r="D1653" s="309">
         <v>2.7E-2</v>
       </c>
-      <c r="E1653" s="309" t="s">
+      <c r="E1653" s="308" t="s">
         <v>45</v>
       </c>
       <c r="F1653" s="354"/>
       <c r="G1653" s="307" t="s">
         <v>628</v>
       </c>
-      <c r="H1653" s="309" t="s">
+      <c r="H1653" s="308" t="s">
         <v>416</v>
       </c>
-      <c r="I1653" s="309"/>
-    </row>
-    <row r="1654" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1654" s="331">
+      <c r="I1653" s="308"/>
+    </row>
+    <row r="1654" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1654" s="330">
         <f>MAX(A1591:A1653)+1</f>
         <v>309</v>
       </c>
@@ -46423,18 +46438,21 @@
       <c r="E1654" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="F1654" s="333" t="s">
+      <c r="F1654" s="332" t="s">
         <v>645</v>
       </c>
       <c r="G1654" s="94" t="s">
         <v>631</v>
       </c>
-      <c r="H1654" s="311"/>
+      <c r="H1654" s="310"/>
       <c r="I1654" s="183"/>
-    </row>
-    <row r="1655" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1655" s="332"/>
-      <c r="B1655" s="314" t="s">
+      <c r="M1654" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1655" s="331"/>
+      <c r="B1655" s="313" t="s">
         <v>630</v>
       </c>
       <c r="C1655" s="154" t="s">
@@ -46446,19 +46464,22 @@
       <c r="E1655" s="156" t="s">
         <v>13</v>
       </c>
-      <c r="F1655" s="334"/>
+      <c r="F1655" s="333"/>
       <c r="G1655" s="156" t="s">
         <v>631</v>
       </c>
-      <c r="H1655" s="315"/>
-      <c r="I1655" s="316"/>
-    </row>
-    <row r="1656" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1656" s="341">
+      <c r="H1655" s="314"/>
+      <c r="I1655" s="315"/>
+      <c r="M1655" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1656" s="340">
         <f>MAX(A1593:A1655)+1</f>
         <v>310</v>
       </c>
-      <c r="B1656" s="322" t="s">
+      <c r="B1656" s="321" t="s">
         <v>630</v>
       </c>
       <c r="C1656" s="257" t="s">
@@ -46470,18 +46491,21 @@
       <c r="E1656" s="256" t="s">
         <v>13</v>
       </c>
-      <c r="F1656" s="345" t="s">
+      <c r="F1656" s="344" t="s">
         <v>642</v>
       </c>
       <c r="G1656" s="256" t="s">
         <v>631</v>
       </c>
-      <c r="H1656" s="319"/>
-      <c r="I1656" s="325"/>
-    </row>
-    <row r="1657" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1657" s="342"/>
-      <c r="B1657" s="323" t="s">
+      <c r="H1656" s="318"/>
+      <c r="I1656" s="324"/>
+      <c r="M1656" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1657" s="341"/>
+      <c r="B1657" s="322" t="s">
         <v>630</v>
       </c>
       <c r="C1657" s="253" t="s">
@@ -46493,40 +46517,46 @@
       <c r="E1657" s="252" t="s">
         <v>13</v>
       </c>
-      <c r="F1657" s="346"/>
+      <c r="F1657" s="345"/>
       <c r="G1657" s="252" t="s">
         <v>631</v>
       </c>
-      <c r="H1657" s="320" t="s">
+      <c r="H1657" s="319" t="s">
         <v>416</v>
       </c>
-      <c r="I1657" s="326"/>
-    </row>
-    <row r="1658" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1658" s="343"/>
-      <c r="B1658" s="324" t="s">
+      <c r="I1657" s="325"/>
+      <c r="M1657" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1658" s="342"/>
+      <c r="B1658" s="323" t="s">
         <v>630</v>
       </c>
-      <c r="C1658" s="318" t="s">
+      <c r="C1658" s="317" t="s">
         <v>632</v>
       </c>
       <c r="D1658" s="291">
         <v>1.5649999999999999</v>
       </c>
-      <c r="E1658" s="317" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1658" s="347"/>
-      <c r="G1658" s="317" t="s">
+      <c r="E1658" s="316" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1658" s="346"/>
+      <c r="G1658" s="316" t="s">
         <v>631</v>
       </c>
-      <c r="H1658" s="321" t="s">
+      <c r="H1658" s="320" t="s">
         <v>416</v>
       </c>
-      <c r="I1658" s="327"/>
-    </row>
-    <row r="1659" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1659" s="331">
+      <c r="I1658" s="326"/>
+      <c r="M1658" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1659" s="330">
         <f>MAX(A1596:A1658)+1</f>
         <v>311</v>
       </c>
@@ -46542,17 +46572,17 @@
       <c r="E1659" s="94" t="s">
         <v>619</v>
       </c>
-      <c r="F1659" s="333" t="s">
+      <c r="F1659" s="332" t="s">
         <v>645</v>
       </c>
       <c r="G1659" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="H1659" s="311"/>
+      <c r="H1659" s="310"/>
       <c r="I1659" s="183"/>
     </row>
-    <row r="1660" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1660" s="344"/>
+    <row r="1660" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1660" s="343"/>
       <c r="B1660" s="244" t="s">
         <v>630</v>
       </c>
@@ -46565,16 +46595,16 @@
       <c r="E1660" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="F1660" s="348"/>
+      <c r="F1660" s="347"/>
       <c r="G1660" s="146" t="s">
         <v>634</v>
       </c>
-      <c r="H1660" s="312"/>
-      <c r="I1660" s="313"/>
-    </row>
-    <row r="1661" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1661" s="332"/>
-      <c r="B1661" s="314" t="s">
+      <c r="H1660" s="311"/>
+      <c r="I1660" s="312"/>
+    </row>
+    <row r="1661" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1661" s="331"/>
+      <c r="B1661" s="313" t="s">
         <v>630</v>
       </c>
       <c r="C1661" s="154" t="s">
@@ -46586,19 +46616,19 @@
       <c r="E1661" s="156" t="s">
         <v>13</v>
       </c>
-      <c r="F1661" s="334"/>
+      <c r="F1661" s="333"/>
       <c r="G1661" s="156" t="s">
         <v>634</v>
       </c>
-      <c r="H1661" s="315"/>
-      <c r="I1661" s="316"/>
-    </row>
-    <row r="1662" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1662" s="341">
+      <c r="H1661" s="314"/>
+      <c r="I1661" s="315"/>
+    </row>
+    <row r="1662" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1662" s="340">
         <f>MAX(A1599:A1661)+1</f>
         <v>312</v>
       </c>
-      <c r="B1662" s="322" t="s">
+      <c r="B1662" s="321" t="s">
         <v>630</v>
       </c>
       <c r="C1662" s="257" t="s">
@@ -46610,20 +46640,23 @@
       <c r="E1662" s="256" t="s">
         <v>13</v>
       </c>
-      <c r="F1662" s="345" t="s">
+      <c r="F1662" s="344" t="s">
         <v>642</v>
       </c>
       <c r="G1662" s="256" t="s">
         <v>634</v>
       </c>
-      <c r="H1662" s="319" t="s">
+      <c r="H1662" s="318" t="s">
         <v>416</v>
       </c>
-      <c r="I1662" s="325"/>
-    </row>
-    <row r="1663" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1663" s="342"/>
-      <c r="B1663" s="323" t="s">
+      <c r="I1662" s="324"/>
+      <c r="M1662" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1663" s="341"/>
+      <c r="B1663" s="322" t="s">
         <v>630</v>
       </c>
       <c r="C1663" s="253" t="s">
@@ -46635,16 +46668,19 @@
       <c r="E1663" s="252" t="s">
         <v>13</v>
       </c>
-      <c r="F1663" s="346"/>
+      <c r="F1663" s="345"/>
       <c r="G1663" s="252" t="s">
         <v>634</v>
       </c>
-      <c r="H1663" s="320"/>
-      <c r="I1663" s="326"/>
-    </row>
-    <row r="1664" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1664" s="342"/>
-      <c r="B1664" s="323" t="s">
+      <c r="H1663" s="319"/>
+      <c r="I1663" s="325"/>
+      <c r="M1663" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1664" s="341"/>
+      <c r="B1664" s="322" t="s">
         <v>630</v>
       </c>
       <c r="C1664" s="253" t="s">
@@ -46656,16 +46692,19 @@
       <c r="E1664" s="252" t="s">
         <v>619</v>
       </c>
-      <c r="F1664" s="346"/>
+      <c r="F1664" s="345"/>
       <c r="G1664" s="252" t="s">
         <v>634</v>
       </c>
-      <c r="H1664" s="320"/>
-      <c r="I1664" s="326"/>
-    </row>
-    <row r="1665" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1665" s="342"/>
-      <c r="B1665" s="328" t="s">
+      <c r="H1664" s="319"/>
+      <c r="I1664" s="325"/>
+      <c r="M1664" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1665" s="341"/>
+      <c r="B1665" s="327" t="s">
         <v>630</v>
       </c>
       <c r="C1665" s="261" t="s">
@@ -46677,15 +46716,15 @@
       <c r="E1665" s="260" t="s">
         <v>619</v>
       </c>
-      <c r="F1665" s="346"/>
+      <c r="F1665" s="345"/>
       <c r="G1665" s="260" t="s">
         <v>634</v>
       </c>
-      <c r="H1665" s="329"/>
-      <c r="I1665" s="330"/>
-    </row>
-    <row r="1666" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A1666" s="335">
+      <c r="H1665" s="328"/>
+      <c r="I1665" s="329"/>
+    </row>
+    <row r="1666" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1666" s="334">
         <f>MAX(A1603:A1665)+1</f>
         <v>313</v>
       </c>
@@ -46701,17 +46740,17 @@
       <c r="E1666" s="94" t="s">
         <v>638</v>
       </c>
-      <c r="F1666" s="338" t="s">
+      <c r="F1666" s="337" t="s">
         <v>639</v>
       </c>
       <c r="G1666" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="H1666" s="311"/>
+      <c r="H1666" s="310"/>
       <c r="I1666" s="183"/>
     </row>
-    <row r="1667" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A1667" s="336"/>
+    <row r="1667" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1667" s="335"/>
       <c r="B1667" s="244" t="s">
         <v>637</v>
       </c>
@@ -46724,15 +46763,15 @@
       <c r="E1667" s="146" t="s">
         <v>638</v>
       </c>
-      <c r="F1667" s="339"/>
+      <c r="F1667" s="338"/>
       <c r="G1667" s="146" t="s">
         <v>634</v>
       </c>
-      <c r="H1667" s="312"/>
-      <c r="I1667" s="313"/>
-    </row>
-    <row r="1668" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A1668" s="336"/>
+      <c r="H1667" s="311"/>
+      <c r="I1667" s="312"/>
+    </row>
+    <row r="1668" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1668" s="335"/>
       <c r="B1668" s="244" t="s">
         <v>637</v>
       </c>
@@ -46745,21 +46784,18 @@
       <c r="E1668" s="146" t="s">
         <v>638</v>
       </c>
-      <c r="F1668" s="339"/>
+      <c r="F1668" s="338"/>
       <c r="G1668" s="146" t="s">
         <v>634</v>
       </c>
-      <c r="H1668" s="312" t="s">
+      <c r="H1668" s="311" t="s">
         <v>416</v>
       </c>
-      <c r="I1668" s="313"/>
-      <c r="J1668" s="308"/>
-      <c r="K1668" s="308"/>
-      <c r="L1668" s="308"/>
-    </row>
-    <row r="1669" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1669" s="337"/>
-      <c r="B1669" s="314" t="s">
+      <c r="I1668" s="312"/>
+    </row>
+    <row r="1669" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1669" s="336"/>
+      <c r="B1669" s="313" t="s">
         <v>643</v>
       </c>
       <c r="C1669" s="154" t="s">
@@ -46771,19 +46807,19 @@
       <c r="E1669" s="156" t="s">
         <v>644</v>
       </c>
-      <c r="F1669" s="340"/>
+      <c r="F1669" s="339"/>
       <c r="G1669" s="156" t="s">
         <v>634</v>
       </c>
-      <c r="H1669" s="315"/>
-      <c r="I1669" s="316"/>
-    </row>
-    <row r="1670" spans="1:12" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1670" s="341">
+      <c r="H1669" s="314"/>
+      <c r="I1669" s="315"/>
+    </row>
+    <row r="1670" spans="1:9" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1670" s="340">
         <f>MAX(A1606:A1669)+1</f>
         <v>314</v>
       </c>
-      <c r="B1670" s="322" t="s">
+      <c r="B1670" s="321" t="s">
         <v>637</v>
       </c>
       <c r="C1670" s="257" t="s">
@@ -46795,41 +46831,38 @@
       <c r="E1670" s="256" t="s">
         <v>638</v>
       </c>
-      <c r="F1670" s="345" t="s">
+      <c r="F1670" s="344" t="s">
         <v>640</v>
       </c>
       <c r="G1670" s="256" t="s">
         <v>634</v>
       </c>
-      <c r="H1670" s="319"/>
-      <c r="I1670" s="325"/>
-    </row>
-    <row r="1671" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1671" s="437"/>
-      <c r="B1671" s="324" t="s">
+      <c r="H1670" s="318"/>
+      <c r="I1670" s="324"/>
+    </row>
+    <row r="1671" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1671" s="348"/>
+      <c r="B1671" s="323" t="s">
         <v>643</v>
       </c>
-      <c r="C1671" s="318" t="s">
+      <c r="C1671" s="317" t="s">
         <v>17</v>
       </c>
       <c r="D1671" s="291">
         <v>0.17399999999999999</v>
       </c>
-      <c r="E1671" s="317" t="s">
+      <c r="E1671" s="316" t="s">
         <v>644</v>
       </c>
-      <c r="F1671" s="347"/>
-      <c r="G1671" s="317" t="s">
+      <c r="F1671" s="346"/>
+      <c r="G1671" s="316" t="s">
         <v>634</v>
       </c>
-      <c r="H1671" s="321"/>
-      <c r="I1671" s="327"/>
-      <c r="J1671" s="308"/>
-      <c r="K1671" s="308"/>
-      <c r="L1671" s="308"/>
-    </row>
-    <row r="1672" spans="1:12" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1672" s="331">
+      <c r="H1671" s="320"/>
+      <c r="I1671" s="326"/>
+    </row>
+    <row r="1672" spans="1:9" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1672" s="330">
         <f>MAX(A1608:A1671)+1</f>
         <v>315</v>
       </c>
@@ -46845,18 +46878,18 @@
       <c r="E1672" s="94" t="s">
         <v>638</v>
       </c>
-      <c r="F1672" s="333" t="s">
+      <c r="F1672" s="332" t="s">
         <v>641</v>
       </c>
       <c r="G1672" s="94" t="s">
         <v>634</v>
       </c>
-      <c r="H1672" s="311"/>
+      <c r="H1672" s="310"/>
       <c r="I1672" s="183"/>
     </row>
-    <row r="1673" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1673" s="332"/>
-      <c r="B1673" s="314" t="s">
+    <row r="1673" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1673" s="331"/>
+      <c r="B1673" s="313" t="s">
         <v>643</v>
       </c>
       <c r="C1673" s="154" t="s">
@@ -46868,12 +46901,12 @@
       <c r="E1673" s="156" t="s">
         <v>644</v>
       </c>
-      <c r="F1673" s="334"/>
+      <c r="F1673" s="333"/>
       <c r="G1673" s="156" t="s">
         <v>634</v>
       </c>
-      <c r="H1673" s="315"/>
-      <c r="I1673" s="316"/>
+      <c r="H1673" s="314"/>
+      <c r="I1673" s="315"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:M1658" xr:uid="{00000000-0009-0000-0000-000000000000}">

--- a/графики/график Останкино.xlsx
+++ b/графики/график Останкино.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE0FA19-D16F-4509-B36B-FAD3435ED062}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13942B3D-23D4-411E-9598-D24706F1D97D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,10 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$2:$M$1658</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$2:$M$1694</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$A$1:$H$1329</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -6458,7 +6458,7 @@
       <c r="K56" s="27"/>
       <c r="L56" s="27"/>
     </row>
-    <row r="57" spans="1:13" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="427">
         <f>MAX(A56,A55,A54,A53,A52,A51,A50,A49,A48,A47,A46,A45)+1</f>
         <v>18</v>
@@ -6979,7 +6979,7 @@
       <c r="K74" s="27"/>
       <c r="L74" s="27"/>
     </row>
-    <row r="75" spans="1:12" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="435"/>
       <c r="B75" s="138" t="s">
         <v>66</v>
@@ -7060,7 +7060,7 @@
       <c r="K77" s="27"/>
       <c r="L77" s="27"/>
     </row>
-    <row r="78" spans="1:12" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="428"/>
       <c r="B78" s="138" t="s">
         <v>66</v>
@@ -7469,7 +7469,7 @@
         <v>05,24</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="427">
         <f>MAX(A93,A92,A91,A90,A89,A88,A87,A86,A85,A84,A83,A82)+1</f>
         <v>28</v>
@@ -9617,7 +9617,7 @@
         <v>07,24</v>
       </c>
     </row>
-    <row r="180" spans="1:13" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="427">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -9649,7 +9649,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="428"/>
       <c r="B181" s="175" t="s">
         <v>119</v>
@@ -10458,7 +10458,7 @@
         <v>07,24</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="421"/>
       <c r="B213" s="126" t="s">
         <v>133</v>
@@ -11240,7 +11240,7 @@
         <v>08,24</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="428"/>
       <c r="B244" s="138" t="s">
         <v>148</v>
@@ -11266,7 +11266,7 @@
         <v>08,24</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="428"/>
       <c r="B245" s="140" t="s">
         <v>148</v>
@@ -11543,7 +11543,7 @@
         <v>08,24</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="421"/>
       <c r="B256" s="108" t="s">
         <v>154</v>
@@ -11745,7 +11745,7 @@
         <v>09,24</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="421"/>
       <c r="B264" s="126" t="s">
         <v>161</v>
@@ -11771,7 +11771,7 @@
         <v>09,24</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="421"/>
       <c r="B265" s="127" t="s">
         <v>161</v>
@@ -12322,7 +12322,7 @@
         <v>09,24</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="427">
         <f t="shared" si="5"/>
         <v>70</v>
@@ -12351,7 +12351,7 @@
         <v>09,24</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="428"/>
       <c r="B288" s="140" t="s">
         <v>171</v>
@@ -12776,7 +12776,7 @@
         <v>09,24</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="427">
         <f>MAX(A304,A303,A302,A301,A300,A299,A298,A297,A296,A295,A294,A293,A292,A291)+1</f>
         <v>74</v>
@@ -13312,7 +13312,7 @@
         <v>10,24</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="42.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" ht="42.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="427">
         <f t="shared" si="7"/>
         <v>80</v>
@@ -13341,7 +13341,7 @@
         <v>10,24</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="42.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" ht="42.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="428"/>
       <c r="B327" s="175" t="s">
         <v>194</v>
@@ -16423,7 +16423,7 @@
         <v>12,24</v>
       </c>
     </row>
-    <row r="450" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="421"/>
       <c r="B450" s="127" t="s">
         <v>238</v>
@@ -17091,7 +17091,7 @@
         <v>01,25</v>
       </c>
     </row>
-    <row r="477" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="412">
         <f t="shared" si="11"/>
         <v>106</v>
@@ -17120,7 +17120,7 @@
         <v>01,25</v>
       </c>
     </row>
-    <row r="478" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="413"/>
       <c r="B478" s="136" t="s">
         <v>250</v>
@@ -17144,7 +17144,7 @@
         <v>01,25</v>
       </c>
     </row>
-    <row r="479" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="413"/>
       <c r="B479" s="136" t="s">
         <v>250</v>
@@ -17168,7 +17168,7 @@
         <v>01,25</v>
       </c>
     </row>
-    <row r="480" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="413"/>
       <c r="B480" s="136" t="s">
         <v>250</v>
@@ -17192,7 +17192,7 @@
         <v>01,25</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="413"/>
       <c r="B481" s="136" t="s">
         <v>250</v>
@@ -18790,7 +18790,7 @@
         <v>02,25</v>
       </c>
     </row>
-    <row r="545" spans="1:9" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="420">
         <f t="shared" si="12"/>
         <v>119</v>
@@ -19641,7 +19641,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="579" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="420">
         <f t="shared" si="12"/>
         <v>125</v>
@@ -19670,7 +19670,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="580" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="421"/>
       <c r="B580" s="108" t="s">
         <v>290</v>
@@ -19989,7 +19989,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="593" spans="1:9" ht="47.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" ht="47.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="420">
         <f t="shared" si="12"/>
         <v>127</v>
@@ -20361,7 +20361,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="608" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="420">
         <f t="shared" si="13"/>
         <v>129</v>
@@ -20390,7 +20390,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="609" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="421"/>
       <c r="B609" s="108" t="s">
         <v>302</v>
@@ -20414,7 +20414,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="610" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="421"/>
       <c r="B610" s="108" t="s">
         <v>302</v>
@@ -20563,7 +20563,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="616" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="420">
         <f t="shared" si="13"/>
         <v>131</v>
@@ -20688,7 +20688,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="621" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="427">
         <f t="shared" si="13"/>
         <v>132</v>
@@ -20717,7 +20717,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="622" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="428"/>
       <c r="B622" s="175" t="s">
         <v>307</v>
@@ -20741,7 +20741,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="623" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="428"/>
       <c r="B623" s="175" t="s">
         <v>307</v>
@@ -20765,7 +20765,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="624" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="428"/>
       <c r="B624" s="175" t="s">
         <v>307</v>
@@ -20789,7 +20789,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="625" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="428"/>
       <c r="B625" s="175" t="s">
         <v>307</v>
@@ -20813,7 +20813,7 @@
         <v>03,25</v>
       </c>
     </row>
-    <row r="626" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="428"/>
       <c r="B626" s="175" t="s">
         <v>307</v>
@@ -21087,7 +21087,7 @@
         <v>04,25</v>
       </c>
     </row>
-    <row r="637" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="428"/>
       <c r="B637" s="175" t="s">
         <v>313</v>
@@ -21113,7 +21113,7 @@
         <v>04,25</v>
       </c>
     </row>
-    <row r="638" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="428"/>
       <c r="B638" s="175" t="s">
         <v>313</v>
@@ -21137,7 +21137,7 @@
         <v>04,25</v>
       </c>
     </row>
-    <row r="639" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="428"/>
       <c r="B639" s="175" t="s">
         <v>313</v>
@@ -22110,7 +22110,7 @@
         <v>04,25</v>
       </c>
     </row>
-    <row r="678" spans="1:9" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="427">
         <f t="shared" si="15"/>
         <v>142</v>
@@ -22139,7 +22139,7 @@
         <v>04,25</v>
       </c>
     </row>
-    <row r="679" spans="1:9" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="428"/>
       <c r="B679" s="140" t="s">
         <v>333</v>
@@ -24071,7 +24071,7 @@
         <v>06,25</v>
       </c>
     </row>
-    <row r="756" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A756" s="420">
         <f t="shared" ref="A756" si="18">MAX(A743:A755)+1</f>
         <v>159</v>
@@ -24100,7 +24100,7 @@
         <v>06,25</v>
       </c>
     </row>
-    <row r="757" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A757" s="421"/>
       <c r="B757" s="127" t="s">
         <v>369</v>
@@ -24124,7 +24124,7 @@
         <v>06,25</v>
       </c>
     </row>
-    <row r="758" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A758" s="421"/>
       <c r="B758" s="127" t="s">
         <v>369</v>
@@ -24196,7 +24196,7 @@
         <v>06,25</v>
       </c>
     </row>
-    <row r="761" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A761" s="421"/>
       <c r="B761" s="126" t="s">
         <v>363</v>
@@ -27118,7 +27118,7 @@
         <v>08,25</v>
       </c>
     </row>
-    <row r="878" spans="1:9" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A878" s="427">
         <f t="shared" si="20"/>
         <v>178</v>
@@ -27147,7 +27147,7 @@
         <v>08,25</v>
       </c>
     </row>
-    <row r="879" spans="1:9" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A879" s="428"/>
       <c r="B879" s="140" t="s">
         <v>410</v>
@@ -27821,7 +27821,7 @@
         <v>08,25</v>
       </c>
     </row>
-    <row r="906" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A906" s="420">
         <f t="shared" ref="A906:A965" si="21">MAX(A883:A905)+1</f>
         <v>183</v>
@@ -27850,7 +27850,7 @@
         <v>08,25</v>
       </c>
     </row>
-    <row r="907" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A907" s="421"/>
       <c r="B907" s="127" t="s">
         <v>421</v>
@@ -28246,7 +28246,7 @@
         <v>08,25</v>
       </c>
     </row>
-    <row r="923" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A923" s="427">
         <f t="shared" si="21"/>
         <v>186</v>
@@ -28275,7 +28275,7 @@
         <v>08,25</v>
       </c>
     </row>
-    <row r="924" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A924" s="428"/>
       <c r="B924" s="175" t="s">
         <v>427</v>
@@ -28299,7 +28299,7 @@
         <v>08,25</v>
       </c>
     </row>
-    <row r="925" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A925" s="428"/>
       <c r="B925" s="175" t="s">
         <v>427</v>
@@ -31003,7 +31003,7 @@
         <v>10,25</v>
       </c>
     </row>
-    <row r="1033" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1033" s="420">
         <v>200</v>
       </c>
@@ -31129,7 +31129,7 @@
         <v>10,25</v>
       </c>
     </row>
-    <row r="1038" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1038" s="427">
         <v>201</v>
       </c>
@@ -32256,7 +32256,7 @@
         <v>10,25</v>
       </c>
     </row>
-    <row r="1083" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1083" s="427">
         <f t="shared" si="24"/>
         <v>210</v>
@@ -32510,7 +32510,7 @@
         <v>11,25</v>
       </c>
     </row>
-    <row r="1093" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1093" s="427">
         <f t="shared" si="24"/>
         <v>212</v>
@@ -39847,7 +39847,7 @@
         <v>03,26</v>
       </c>
     </row>
-    <row r="1386" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1386" spans="1:9" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1386" s="417">
         <f>MAX(A1313:A1382)+1</f>
         <v>260</v>
@@ -47576,7 +47576,7 @@
       <c r="I1694" s="71"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M1658" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A2:M1694" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="8">
       <filters blank="1"/>
     </filterColumn>

--- a/графики/график Останкино.xlsx
+++ b/графики/график Останкино.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4314A619-855F-4532-A800-72FE816F6C31}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C24F70-F1BA-48E6-9ECC-35B7F0F3CE32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$2:$M$1789</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$2:$M$1810</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$A$1:$H$1329</definedName>
   </definedNames>
   <calcPr calcId="181029" refMode="R1C1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7776" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7855" uniqueCount="740">
   <si>
     <t>№ п/п</t>
   </si>
@@ -2246,6 +2246,27 @@
   </si>
   <si>
     <t>27,08,26</t>
+  </si>
+  <si>
+    <t>02,09,26</t>
+  </si>
+  <si>
+    <t>06,09,26</t>
+  </si>
+  <si>
+    <t>Карлова_Баранова</t>
+  </si>
+  <si>
+    <t>07,09,26</t>
+  </si>
+  <si>
+    <t>08,09,26</t>
+  </si>
+  <si>
+    <t>03,09,26</t>
+  </si>
+  <si>
+    <t>Луганск (сети)</t>
   </si>
 </sst>
 </file>
@@ -3244,7 +3265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="554">
+  <cellXfs count="557">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4452,457 +4473,466 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="11" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="11" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5290,12 +5320,12 @@
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AMF1810"/>
+  <dimension ref="A1:AMF1829"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="368" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="21.42578125" style="4" customWidth="1"/>
@@ -42588,7 +42618,7 @@
         <v>04,26</v>
       </c>
     </row>
-    <row r="1478" spans="1:9" ht="38.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1478" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1478" s="294"/>
       <c r="B1478" s="138" t="s">
         <v>580</v>
@@ -49758,7 +49788,7 @@
       </c>
       <c r="H1750" s="152"/>
       <c r="I1750" s="152" t="str">
-        <f t="shared" ref="I1750:I1760" si="46">RIGHT(G1750,5)</f>
+        <f t="shared" ref="I1750:I1783" si="46">RIGHT(G1750,5)</f>
         <v>08,26</v>
       </c>
     </row>
@@ -50027,7 +50057,7 @@
         <v>08,26</v>
       </c>
     </row>
-    <row r="1761" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="1761" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1761" s="426">
         <f t="shared" si="48"/>
         <v>360</v>
@@ -50051,9 +50081,12 @@
         <v>717</v>
       </c>
       <c r="H1761" s="132"/>
-      <c r="I1761" s="336"/>
-    </row>
-    <row r="1762" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1761" s="132" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1762" s="427"/>
       <c r="B1762" s="390" t="s">
         <v>715</v>
@@ -50072,9 +50105,12 @@
         <v>717</v>
       </c>
       <c r="H1762" s="152"/>
-      <c r="I1762" s="337"/>
-    </row>
-    <row r="1763" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1762" s="152" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1763" s="427"/>
       <c r="B1763" s="390" t="s">
         <v>715</v>
@@ -50093,9 +50129,12 @@
         <v>717</v>
       </c>
       <c r="H1763" s="152"/>
-      <c r="I1763" s="337"/>
-    </row>
-    <row r="1764" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1763" s="152" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1764" s="428"/>
       <c r="B1764" s="95" t="s">
         <v>715</v>
@@ -50114,9 +50153,12 @@
         <v>717</v>
       </c>
       <c r="H1764" s="158"/>
-      <c r="I1764" s="338"/>
-    </row>
-    <row r="1765" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1764" s="158" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1765" s="429">
         <f t="shared" si="48"/>
         <v>361</v>
@@ -50140,9 +50182,12 @@
         <v>718</v>
       </c>
       <c r="H1765" s="107"/>
-      <c r="I1765" s="326"/>
-    </row>
-    <row r="1766" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1765" s="107" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1766" s="430"/>
       <c r="B1766" s="108" t="s">
         <v>715</v>
@@ -50161,9 +50206,12 @@
         <v>718</v>
       </c>
       <c r="H1766" s="219"/>
-      <c r="I1766" s="328"/>
-    </row>
-    <row r="1767" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1766" s="219" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1767" s="431"/>
       <c r="B1767" s="114" t="s">
         <v>715</v>
@@ -50182,9 +50230,12 @@
         <v>718</v>
       </c>
       <c r="H1767" s="220"/>
-      <c r="I1767" s="327"/>
-    </row>
-    <row r="1768" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1767" s="220" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:9" ht="38.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1768" s="339">
         <f t="shared" si="48"/>
         <v>362</v>
@@ -50208,9 +50259,12 @@
         <v>719</v>
       </c>
       <c r="H1768" s="125"/>
-      <c r="I1768" s="395"/>
-    </row>
-    <row r="1769" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="I1768" s="125" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:9" ht="38.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1769" s="429">
         <f t="shared" si="48"/>
         <v>363</v>
@@ -50234,9 +50288,12 @@
         <v>718</v>
       </c>
       <c r="H1769" s="107"/>
-      <c r="I1769" s="326"/>
-    </row>
-    <row r="1770" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1769" s="107" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:9" ht="38.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1770" s="431"/>
       <c r="B1770" s="222" t="s">
         <v>720</v>
@@ -50255,9 +50312,12 @@
         <v>718</v>
       </c>
       <c r="H1770" s="220"/>
-      <c r="I1770" s="327"/>
-    </row>
-    <row r="1771" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1770" s="220" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:9" ht="38.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1771" s="398">
         <f t="shared" si="48"/>
         <v>364</v>
@@ -50281,9 +50341,12 @@
         <v>718</v>
       </c>
       <c r="H1771" s="400"/>
-      <c r="I1771" s="405"/>
-    </row>
-    <row r="1772" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1771" s="422" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1772" s="429">
         <f t="shared" si="48"/>
         <v>365</v>
@@ -50307,9 +50370,12 @@
         <v>722</v>
       </c>
       <c r="H1772" s="107"/>
-      <c r="I1772" s="326"/>
-    </row>
-    <row r="1773" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1772" s="107" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1773" s="430"/>
       <c r="B1773" s="108" t="s">
         <v>721</v>
@@ -50328,9 +50394,12 @@
         <v>722</v>
       </c>
       <c r="H1773" s="219"/>
-      <c r="I1773" s="328"/>
-    </row>
-    <row r="1774" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1773" s="219" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1774" s="431"/>
       <c r="B1774" s="114" t="s">
         <v>721</v>
@@ -50349,9 +50418,12 @@
         <v>722</v>
       </c>
       <c r="H1774" s="220"/>
-      <c r="I1774" s="327"/>
-    </row>
-    <row r="1775" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1774" s="220" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1775" s="426">
         <f t="shared" si="48"/>
         <v>366</v>
@@ -50375,9 +50447,12 @@
         <v>723</v>
       </c>
       <c r="H1775" s="132"/>
-      <c r="I1775" s="336"/>
-    </row>
-    <row r="1776" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I1775" s="132" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1776" s="427"/>
       <c r="B1776" s="402" t="s">
         <v>721</v>
@@ -50396,9 +50471,12 @@
         <v>723</v>
       </c>
       <c r="H1776" s="152"/>
-      <c r="I1776" s="337"/>
-    </row>
-    <row r="1777" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I1776" s="152" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:13" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1777" s="427"/>
       <c r="B1777" s="402" t="s">
         <v>721</v>
@@ -50417,9 +50495,12 @@
         <v>723</v>
       </c>
       <c r="H1777" s="152"/>
-      <c r="I1777" s="337"/>
-    </row>
-    <row r="1778" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1777" s="152" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:13" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1778" s="428"/>
       <c r="B1778" s="95" t="s">
         <v>721</v>
@@ -50438,9 +50519,12 @@
         <v>723</v>
       </c>
       <c r="H1778" s="158"/>
-      <c r="I1778" s="338"/>
-    </row>
-    <row r="1779" spans="1:13" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1778" s="158" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:13" ht="38.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1779" s="329">
         <f t="shared" si="48"/>
         <v>367</v>
@@ -50464,9 +50548,12 @@
         <v>723</v>
       </c>
       <c r="H1779" s="335"/>
-      <c r="I1779" s="406"/>
-    </row>
-    <row r="1780" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I1779" s="335" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:13" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1780" s="426">
         <f t="shared" si="48"/>
         <v>368</v>
@@ -50490,9 +50577,12 @@
         <v>724</v>
       </c>
       <c r="H1780" s="132"/>
-      <c r="I1780" s="336"/>
-    </row>
-    <row r="1781" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1780" s="132" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:13" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1781" s="428"/>
       <c r="B1781" s="95" t="s">
         <v>721</v>
@@ -50511,9 +50601,12 @@
         <v>724</v>
       </c>
       <c r="H1781" s="158"/>
-      <c r="I1781" s="338"/>
-    </row>
-    <row r="1782" spans="1:13" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="I1781" s="158" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:13" ht="38.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1782" s="429">
         <f t="shared" si="48"/>
         <v>369</v>
@@ -50537,11 +50630,14 @@
         <v>723</v>
       </c>
       <c r="H1782" s="107"/>
-      <c r="I1782" s="326"/>
-    </row>
-    <row r="1783" spans="1:13" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1782" s="107" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:13" ht="38.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1783" s="431"/>
-      <c r="B1783" s="408" t="s">
+      <c r="B1783" s="406" t="s">
         <v>725</v>
       </c>
       <c r="C1783" s="225" t="s">
@@ -50550,22 +50646,25 @@
       <c r="D1783" s="226">
         <v>0.67200000000000004</v>
       </c>
-      <c r="E1783" s="409" t="s">
+      <c r="E1783" s="407" t="s">
         <v>638</v>
       </c>
       <c r="F1783" s="436"/>
-      <c r="G1783" s="409" t="s">
+      <c r="G1783" s="407" t="s">
         <v>723</v>
       </c>
-      <c r="H1783" s="410"/>
-      <c r="I1783" s="411"/>
+      <c r="H1783" s="408"/>
+      <c r="I1783" s="408" t="str">
+        <f t="shared" si="46"/>
+        <v>08,26</v>
+      </c>
     </row>
     <row r="1784" spans="1:13" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A1784" s="552">
         <f t="shared" si="48"/>
         <v>370</v>
       </c>
-      <c r="B1784" s="407" t="s">
+      <c r="B1784" s="405" t="s">
         <v>725</v>
       </c>
       <c r="C1784" s="92" t="s">
@@ -50588,34 +50687,34 @@
     </row>
     <row r="1785" spans="1:13" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1785" s="553"/>
-      <c r="B1785" s="415" t="s">
+      <c r="B1785" s="412" t="s">
         <v>725</v>
       </c>
-      <c r="C1785" s="416" t="s">
+      <c r="C1785" s="413" t="s">
         <v>367</v>
       </c>
-      <c r="D1785" s="417">
+      <c r="D1785" s="414">
         <v>1.6080000000000001</v>
       </c>
-      <c r="E1785" s="418" t="s">
+      <c r="E1785" s="415" t="s">
         <v>638</v>
       </c>
       <c r="F1785" s="551"/>
-      <c r="G1785" s="418" t="s">
+      <c r="G1785" s="415" t="s">
         <v>723</v>
       </c>
-      <c r="H1785" s="419"/>
-      <c r="I1785" s="420"/>
-      <c r="J1785" s="404"/>
-      <c r="K1785" s="404"/>
-      <c r="L1785" s="404"/>
-      <c r="M1785" s="421" t="s">
+      <c r="H1785" s="416"/>
+      <c r="I1785" s="417"/>
+      <c r="J1785" s="403"/>
+      <c r="K1785" s="403"/>
+      <c r="L1785" s="403"/>
+      <c r="M1785" s="418" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="1786" spans="1:13" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1786" s="412">
-        <f t="shared" ref="A1786:A1810" si="49">MAX(A1720:A1785)+1</f>
+      <c r="A1786" s="409">
+        <f t="shared" ref="A1786:A1829" si="49">MAX(A1720:A1785)+1</f>
         <v>371</v>
       </c>
       <c r="B1786" s="164" t="s">
@@ -50630,14 +50729,14 @@
       <c r="E1786" s="167" t="s">
         <v>638</v>
       </c>
-      <c r="F1786" s="413" t="s">
+      <c r="F1786" s="410" t="s">
         <v>726</v>
       </c>
       <c r="G1786" s="167" t="s">
         <v>723</v>
       </c>
-      <c r="H1786" s="414"/>
-      <c r="I1786" s="425"/>
+      <c r="H1786" s="411"/>
+      <c r="I1786" s="421"/>
     </row>
     <row r="1787" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1787" s="426">
@@ -50982,7 +51081,7 @@
         <v>729</v>
       </c>
       <c r="H1801" s="335"/>
-      <c r="I1801" s="406"/>
+      <c r="I1801" s="404"/>
     </row>
     <row r="1802" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1802" s="339">
@@ -51011,124 +51110,555 @@
       <c r="I1802" s="395"/>
     </row>
     <row r="1803" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1803" s="403">
+      <c r="A1803" s="429">
         <f t="shared" si="49"/>
         <v>379</v>
       </c>
-      <c r="B1803" s="27"/>
-      <c r="C1803" s="422"/>
-      <c r="D1803" s="423"/>
-      <c r="E1803" s="27"/>
-      <c r="F1803" s="424"/>
-      <c r="G1803" s="27"/>
-      <c r="H1803" s="403"/>
-      <c r="I1803" s="27"/>
+      <c r="B1803" s="102" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1803" s="103" t="s">
+        <v>735</v>
+      </c>
+      <c r="D1803" s="104">
+        <v>1.9079999999999999</v>
+      </c>
+      <c r="E1803" s="105" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1803" s="435" t="s">
+        <v>642</v>
+      </c>
+      <c r="G1803" s="105" t="s">
+        <v>734</v>
+      </c>
+      <c r="H1803" s="107"/>
+      <c r="I1803" s="326"/>
     </row>
     <row r="1804" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1804" s="322">
+      <c r="A1804" s="430"/>
+      <c r="B1804" s="108" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1804" s="109" t="s">
+        <v>564</v>
+      </c>
+      <c r="D1804" s="110">
+        <v>1.22</v>
+      </c>
+      <c r="E1804" s="111" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1804" s="436"/>
+      <c r="G1804" s="111" t="s">
+        <v>734</v>
+      </c>
+      <c r="H1804" s="219"/>
+      <c r="I1804" s="328"/>
+    </row>
+    <row r="1805" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1805" s="430"/>
+      <c r="B1805" s="108" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1805" s="109" t="s">
+        <v>367</v>
+      </c>
+      <c r="D1805" s="110">
+        <v>1.7549999999999999</v>
+      </c>
+      <c r="E1805" s="111" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1805" s="436"/>
+      <c r="G1805" s="111" t="s">
+        <v>734</v>
+      </c>
+      <c r="H1805" s="219"/>
+      <c r="I1805" s="328"/>
+    </row>
+    <row r="1806" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1806" s="430"/>
+      <c r="B1806" s="164" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1806" s="165" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1806" s="166">
+        <v>5.1840000000000002</v>
+      </c>
+      <c r="E1806" s="167" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1806" s="436"/>
+      <c r="G1806" s="167" t="s">
+        <v>734</v>
+      </c>
+      <c r="H1806" s="408"/>
+      <c r="I1806" s="555"/>
+    </row>
+    <row r="1807" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1807" s="426">
         <f t="shared" si="49"/>
         <v>380</v>
       </c>
-      <c r="B1804" s="71"/>
-      <c r="C1804" s="323"/>
-      <c r="D1804" s="324"/>
-      <c r="E1804" s="71"/>
-      <c r="F1804" s="325"/>
-      <c r="G1804" s="71"/>
-      <c r="H1804" s="322"/>
-      <c r="I1804" s="71"/>
-    </row>
-    <row r="1805" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1805" s="322">
+      <c r="B1807" s="91" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1807" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1807" s="93">
+        <v>4.883</v>
+      </c>
+      <c r="E1807" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1807" s="432" t="s">
+        <v>642</v>
+      </c>
+      <c r="G1807" s="94" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1807" s="132"/>
+      <c r="I1807" s="336"/>
+    </row>
+    <row r="1808" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1808" s="427"/>
+      <c r="B1808" s="423" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1808" s="147" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1808" s="148">
+        <v>9.4E-2</v>
+      </c>
+      <c r="E1808" s="146" t="s">
+        <v>619</v>
+      </c>
+      <c r="F1808" s="433"/>
+      <c r="G1808" s="146" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1808" s="152"/>
+      <c r="I1808" s="337"/>
+    </row>
+    <row r="1809" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1809" s="427"/>
+      <c r="B1809" s="423" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1809" s="147" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1809" s="148">
+        <v>5.2610000000000001</v>
+      </c>
+      <c r="E1809" s="136" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1809" s="433"/>
+      <c r="G1809" s="146" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1809" s="152"/>
+      <c r="I1809" s="337"/>
+    </row>
+    <row r="1810" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1810" s="428"/>
+      <c r="B1810" s="95" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1810" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1810" s="155">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="E1810" s="156" t="s">
+        <v>619</v>
+      </c>
+      <c r="F1810" s="434"/>
+      <c r="G1810" s="156" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1810" s="158"/>
+      <c r="I1810" s="338"/>
+    </row>
+    <row r="1811" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1811" s="430">
         <f t="shared" si="49"/>
         <v>381</v>
       </c>
-      <c r="B1805" s="71"/>
-      <c r="C1805" s="323"/>
-      <c r="D1805" s="324"/>
-      <c r="E1805" s="71"/>
-      <c r="F1805" s="325"/>
-      <c r="G1805" s="71"/>
-      <c r="H1805" s="322"/>
-      <c r="I1805" s="71"/>
-    </row>
-    <row r="1806" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1806" s="322">
+      <c r="B1811" s="108" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1811" s="109" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1811" s="110">
+        <v>5.1420000000000003</v>
+      </c>
+      <c r="E1811" s="111" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1811" s="436" t="s">
+        <v>645</v>
+      </c>
+      <c r="G1811" s="111" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1811" s="113"/>
+      <c r="I1811" s="556"/>
+    </row>
+    <row r="1812" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1812" s="430"/>
+      <c r="B1812" s="164" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1812" s="225" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1812" s="226">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="E1812" s="407" t="s">
+        <v>619</v>
+      </c>
+      <c r="F1812" s="436"/>
+      <c r="G1812" s="407" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1812" s="408"/>
+      <c r="I1812" s="555"/>
+    </row>
+    <row r="1813" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1813" s="426">
         <f t="shared" si="49"/>
         <v>382</v>
       </c>
-      <c r="B1806" s="71"/>
-      <c r="C1806" s="323"/>
-      <c r="D1806" s="324"/>
-      <c r="E1806" s="71"/>
-      <c r="F1806" s="325"/>
-      <c r="G1806" s="71"/>
-      <c r="H1806" s="322"/>
-      <c r="I1806" s="71"/>
-    </row>
-    <row r="1807" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1807" s="322">
+      <c r="B1813" s="91" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1813" s="92" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1813" s="93">
+        <v>7.8929999999999998</v>
+      </c>
+      <c r="E1813" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1813" s="432" t="s">
+        <v>645</v>
+      </c>
+      <c r="G1813" s="94" t="s">
+        <v>737</v>
+      </c>
+      <c r="H1813" s="132"/>
+      <c r="I1813" s="336"/>
+    </row>
+    <row r="1814" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1814" s="427"/>
+      <c r="B1814" s="423" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1814" s="147" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1814" s="246">
+        <v>2.3E-2</v>
+      </c>
+      <c r="E1814" s="146" t="s">
+        <v>619</v>
+      </c>
+      <c r="F1814" s="433"/>
+      <c r="G1814" s="146" t="s">
+        <v>737</v>
+      </c>
+      <c r="H1814" s="152"/>
+      <c r="I1814" s="337"/>
+    </row>
+    <row r="1815" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1815" s="428"/>
+      <c r="B1815" s="95" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1815" s="154" t="s">
+        <v>681</v>
+      </c>
+      <c r="D1815" s="155">
+        <v>8.34</v>
+      </c>
+      <c r="E1815" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1815" s="434"/>
+      <c r="G1815" s="156" t="s">
+        <v>737</v>
+      </c>
+      <c r="H1815" s="158"/>
+      <c r="I1815" s="338"/>
+    </row>
+    <row r="1816" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1816" s="430">
         <f t="shared" si="49"/>
         <v>383</v>
       </c>
-      <c r="B1807" s="71"/>
-      <c r="C1807" s="323"/>
-      <c r="D1807" s="324"/>
-      <c r="E1807" s="71"/>
-      <c r="F1807" s="325"/>
-      <c r="G1807" s="71"/>
-      <c r="H1807" s="322"/>
-      <c r="I1807" s="71"/>
-    </row>
-    <row r="1808" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1808" s="322">
+      <c r="B1816" s="108" t="s">
+        <v>738</v>
+      </c>
+      <c r="C1816" s="109" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1816" s="110">
+        <v>1.1579999999999999</v>
+      </c>
+      <c r="E1816" s="111" t="s">
+        <v>638</v>
+      </c>
+      <c r="F1816" s="436" t="s">
+        <v>708</v>
+      </c>
+      <c r="G1816" s="111" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1816" s="113"/>
+      <c r="I1816" s="556"/>
+    </row>
+    <row r="1817" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1817" s="430"/>
+      <c r="B1817" s="406" t="s">
+        <v>738</v>
+      </c>
+      <c r="C1817" s="225" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1817" s="226">
+        <v>8.36</v>
+      </c>
+      <c r="E1817" s="407" t="s">
+        <v>638</v>
+      </c>
+      <c r="F1817" s="436"/>
+      <c r="G1817" s="407" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1817" s="408"/>
+      <c r="I1817" s="555"/>
+    </row>
+    <row r="1818" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1818" s="339">
         <f t="shared" si="49"/>
         <v>384</v>
       </c>
-      <c r="B1808" s="71"/>
-      <c r="C1808" s="323"/>
-      <c r="D1808" s="324"/>
-      <c r="E1808" s="71"/>
-      <c r="F1808" s="325"/>
-      <c r="G1808" s="71"/>
-      <c r="H1808" s="322"/>
-      <c r="I1808" s="71"/>
-    </row>
-    <row r="1809" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1809" s="322">
+      <c r="B1818" s="121" t="s">
+        <v>738</v>
+      </c>
+      <c r="C1818" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1818" s="123">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="E1818" s="124" t="s">
+        <v>638</v>
+      </c>
+      <c r="F1818" s="340" t="s">
+        <v>709</v>
+      </c>
+      <c r="G1818" s="124" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1818" s="125"/>
+      <c r="I1818" s="395"/>
+    </row>
+    <row r="1819" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1819" s="430">
         <f t="shared" si="49"/>
         <v>385</v>
       </c>
-      <c r="B1809" s="71"/>
-      <c r="C1809" s="323"/>
-      <c r="D1809" s="324"/>
-      <c r="E1809" s="71"/>
-      <c r="F1809" s="325"/>
-      <c r="G1809" s="71"/>
-      <c r="H1809" s="322"/>
-      <c r="I1809" s="71"/>
-    </row>
-    <row r="1810" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1810" s="322">
+      <c r="B1819" s="108" t="s">
+        <v>738</v>
+      </c>
+      <c r="C1819" s="109" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1819" s="110">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="E1819" s="111" t="s">
+        <v>638</v>
+      </c>
+      <c r="F1819" s="436" t="s">
+        <v>726</v>
+      </c>
+      <c r="G1819" s="111" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1819" s="113"/>
+      <c r="I1819" s="556"/>
+    </row>
+    <row r="1820" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1820" s="431"/>
+      <c r="B1820" s="222" t="s">
+        <v>738</v>
+      </c>
+      <c r="C1820" s="216" t="s">
+        <v>739</v>
+      </c>
+      <c r="D1820" s="554">
+        <v>2.7E-2</v>
+      </c>
+      <c r="E1820" s="218" t="s">
+        <v>638</v>
+      </c>
+      <c r="F1820" s="437"/>
+      <c r="G1820" s="218" t="s">
+        <v>736</v>
+      </c>
+      <c r="H1820" s="220"/>
+      <c r="I1820" s="327"/>
+    </row>
+    <row r="1821" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1821" s="424">
         <f t="shared" si="49"/>
         <v>386</v>
       </c>
-      <c r="B1810" s="71"/>
-      <c r="C1810" s="323"/>
-      <c r="D1810" s="324"/>
-      <c r="E1810" s="71"/>
-      <c r="F1810" s="325"/>
-      <c r="G1810" s="71"/>
-      <c r="H1810" s="322"/>
-      <c r="I1810" s="71"/>
+      <c r="B1821" s="27"/>
+      <c r="C1821" s="419"/>
+      <c r="D1821" s="420"/>
+      <c r="E1821" s="27"/>
+      <c r="F1821" s="425"/>
+      <c r="G1821" s="27"/>
+      <c r="H1821" s="424"/>
+      <c r="I1821" s="27"/>
+    </row>
+    <row r="1822" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1822" s="322">
+        <f t="shared" si="49"/>
+        <v>387</v>
+      </c>
+      <c r="B1822" s="71"/>
+      <c r="C1822" s="323"/>
+      <c r="D1822" s="324"/>
+      <c r="E1822" s="71"/>
+      <c r="F1822" s="325"/>
+      <c r="G1822" s="71"/>
+      <c r="H1822" s="322"/>
+      <c r="I1822" s="71"/>
+    </row>
+    <row r="1823" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1823" s="322">
+        <f t="shared" si="49"/>
+        <v>388</v>
+      </c>
+      <c r="B1823" s="71"/>
+      <c r="C1823" s="323"/>
+      <c r="D1823" s="324"/>
+      <c r="E1823" s="71"/>
+      <c r="F1823" s="325"/>
+      <c r="G1823" s="71"/>
+      <c r="H1823" s="322"/>
+      <c r="I1823" s="71"/>
+    </row>
+    <row r="1824" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1824" s="322">
+        <f t="shared" si="49"/>
+        <v>389</v>
+      </c>
+      <c r="B1824" s="71"/>
+      <c r="C1824" s="323"/>
+      <c r="D1824" s="324"/>
+      <c r="E1824" s="71"/>
+      <c r="F1824" s="325"/>
+      <c r="G1824" s="71"/>
+      <c r="H1824" s="322"/>
+      <c r="I1824" s="71"/>
+    </row>
+    <row r="1825" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1825" s="322">
+        <f t="shared" si="49"/>
+        <v>390</v>
+      </c>
+      <c r="B1825" s="71"/>
+      <c r="C1825" s="323"/>
+      <c r="D1825" s="324"/>
+      <c r="E1825" s="71"/>
+      <c r="F1825" s="325"/>
+      <c r="G1825" s="71"/>
+      <c r="H1825" s="322"/>
+      <c r="I1825" s="71"/>
+    </row>
+    <row r="1826" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1826" s="322">
+        <f t="shared" si="49"/>
+        <v>391</v>
+      </c>
+      <c r="B1826" s="71"/>
+      <c r="C1826" s="323"/>
+      <c r="D1826" s="324"/>
+      <c r="E1826" s="71"/>
+      <c r="F1826" s="325"/>
+      <c r="G1826" s="71"/>
+      <c r="H1826" s="322"/>
+      <c r="I1826" s="71"/>
+    </row>
+    <row r="1827" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1827" s="322">
+        <f t="shared" si="49"/>
+        <v>392</v>
+      </c>
+      <c r="B1827" s="71"/>
+      <c r="C1827" s="323"/>
+      <c r="D1827" s="324"/>
+      <c r="E1827" s="71"/>
+      <c r="F1827" s="325"/>
+      <c r="G1827" s="71"/>
+      <c r="H1827" s="322"/>
+      <c r="I1827" s="71"/>
+    </row>
+    <row r="1828" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1828" s="322">
+        <f t="shared" si="49"/>
+        <v>393</v>
+      </c>
+      <c r="B1828" s="71"/>
+      <c r="C1828" s="323"/>
+      <c r="D1828" s="324"/>
+      <c r="E1828" s="71"/>
+      <c r="F1828" s="325"/>
+      <c r="G1828" s="71"/>
+      <c r="H1828" s="322"/>
+      <c r="I1828" s="71"/>
+    </row>
+    <row r="1829" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1829" s="322">
+        <f t="shared" si="49"/>
+        <v>394</v>
+      </c>
+      <c r="B1829" s="71"/>
+      <c r="C1829" s="323"/>
+      <c r="D1829" s="324"/>
+      <c r="E1829" s="71"/>
+      <c r="F1829" s="325"/>
+      <c r="G1829" s="71"/>
+      <c r="H1829" s="322"/>
+      <c r="I1829" s="71"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M1789" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A2:M1810" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="8">
       <filters blank="1"/>
     </filterColumn>
   </autoFilter>
-  <mergeCells count="661">
+  <mergeCells count="673">
+    <mergeCell ref="A1816:A1817"/>
+    <mergeCell ref="F1816:F1817"/>
+    <mergeCell ref="F1819:F1820"/>
+    <mergeCell ref="A1819:A1820"/>
     <mergeCell ref="F1784:F1785"/>
     <mergeCell ref="A1784:A1785"/>
     <mergeCell ref="F1688:F1689"/>
@@ -51780,6 +52310,14 @@
     <mergeCell ref="F1741:F1743"/>
     <mergeCell ref="A1744:A1745"/>
     <mergeCell ref="F1744:F1745"/>
+    <mergeCell ref="A1803:A1806"/>
+    <mergeCell ref="F1803:F1806"/>
+    <mergeCell ref="A1807:A1810"/>
+    <mergeCell ref="A1811:A1812"/>
+    <mergeCell ref="F1807:F1810"/>
+    <mergeCell ref="F1811:F1812"/>
+    <mergeCell ref="A1813:A1815"/>
+    <mergeCell ref="F1813:F1815"/>
     <mergeCell ref="A1787:A1789"/>
     <mergeCell ref="A1790:A1793"/>
     <mergeCell ref="A1794:A1795"/>
